--- a/apps/web/public/examples/example-with-constraint-rules.xlsx
+++ b/apps/web/public/examples/example-with-constraint-rules.xlsx
@@ -391,100 +391,100 @@
     <t>EnrollmentDay10</t>
   </si>
   <si>
-    <t>R2-FA-MATH231-A</t>
-  </si>
-  <si>
-    <t>R2</t>
+    <t>AY25-FA-MATH231-A</t>
+  </si>
+  <si>
+    <t>AY25</t>
   </si>
   <si>
     <t>10:20</t>
   </si>
   <si>
-    <t>R2-FA-MATH231-B</t>
+    <t>AY25-FA-MATH231-B</t>
   </si>
   <si>
     <t>11:00</t>
   </si>
   <si>
-    <t>R2-FA-STAT243-A</t>
-  </si>
-  <si>
-    <t>R2-FA-MATH250-A</t>
+    <t>AY25-FA-STAT243-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH250-A</t>
   </si>
   <si>
     <t>09:15</t>
   </si>
   <si>
-    <t>R2-FA-DATA202-A</t>
-  </si>
-  <si>
-    <t>R2-FA-DATA301-A</t>
+    <t>AY25-FA-DATA202-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DATA301-A</t>
   </si>
   <si>
     <t>12:15</t>
   </si>
   <si>
-    <t>R2-FA-STAT343-A</t>
-  </si>
-  <si>
-    <t>R2-FA-CS262-A</t>
+    <t>AY25-FA-STAT343-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-CS262-A</t>
   </si>
   <si>
     <t>13:30</t>
   </si>
   <si>
-    <t>R2-FA-CS108-A</t>
+    <t>AY25-FA-CS108-A</t>
   </si>
   <si>
     <t>14:45</t>
   </si>
   <si>
-    <t>R2-FA-CS372-A</t>
+    <t>AY25-FA-CS372-A</t>
   </si>
   <si>
     <t>16:00</t>
   </si>
   <si>
-    <t>R2-FA-CS108-B</t>
+    <t>AY25-FA-CS108-B</t>
   </si>
   <si>
     <t>08:00</t>
   </si>
   <si>
-    <t>R2-FA-MATH301-A</t>
+    <t>AY25-FA-MATH301-A</t>
   </si>
   <si>
     <t>14:10</t>
   </si>
   <si>
-    <t>R2-FA-MATH290-A</t>
+    <t>AY25-FA-MATH290-A</t>
   </si>
   <si>
     <t>15:05</t>
   </si>
   <si>
-    <t>R2-FA-STAT143-A</t>
-  </si>
-  <si>
-    <t>R2-FA-STAT143-B</t>
-  </si>
-  <si>
-    <t>R2-FA-STAT143-C</t>
+    <t>AY25-FA-STAT143-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-STAT143-B</t>
+  </si>
+  <si>
+    <t>AY25-FA-STAT143-C</t>
   </si>
   <si>
     <t>10:30</t>
   </si>
   <si>
-    <t>R2-FA-CORE100-A</t>
-  </si>
-  <si>
-    <t>R2-FA-CORE100-B</t>
-  </si>
-  <si>
-    <t>R2-SP-MATH232-A</t>
-  </si>
-  <si>
-    <t>R2-SP-STAT244-A</t>
+    <t>AY25-FA-CORE100-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-CORE100-B</t>
+  </si>
+  <si>
+    <t>AY25-SP-MATH232-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-STAT244-A</t>
   </si>
   <si>
     <t>Activity</t>
@@ -799,7 +799,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>10:15:43</t>
+    <t>10:29:00</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -2412,7 +2412,7 @@
   <dimension ref="A1:X21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>

--- a/apps/web/public/examples/example-with-constraint-rules.xlsx
+++ b/apps/web/public/examples/example-with-constraint-rules.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="285">
   <si>
     <t>Term</t>
   </si>
@@ -265,6 +265,21 @@
     <t>Discrete Mathematics</t>
   </si>
   <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:40:00</t>
+  </si>
+  <si>
+    <t>Introductory Linear Algebra</t>
+  </si>
+  <si>
+    <t>Tuesday only: some of the days of TR at 8:00; allowed by this department's subset rule</t>
+  </si>
+  <si>
     <t>290</t>
   </si>
   <si>
@@ -346,6 +361,18 @@
     <t>Regression Models</t>
   </si>
   <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Applied Data Analysis</t>
+  </si>
+  <si>
+    <t>Friday only: some of the days of MWF at 9:15; not covered by the subset rule</t>
+  </si>
+  <si>
     <t>343</t>
   </si>
   <si>
@@ -487,6 +514,12 @@
     <t>AY25-SP-STAT244-A</t>
   </si>
   <si>
+    <t>AY25-SP-MATH255-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-STAT245-A</t>
+  </si>
+  <si>
     <t>Activity</t>
   </si>
   <si>
@@ -700,6 +733,18 @@
     <t>65</t>
   </si>
   <si>
+    <t>Linear algebra may meet one day of TR</t>
+  </si>
+  <si>
+    <t>subset</t>
+  </si>
+  <si>
+    <t>MATH 255</t>
+  </si>
+  <si>
+    <t>MATH 255 is meant to meet on only one of the standard days, so it is not flagged for that.</t>
+  </si>
+  <si>
     <t>Kind</t>
   </si>
   <si>
@@ -799,7 +844,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>10:29:00</t>
+    <t>22:57:57</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -818,6 +863,9 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Default Department</t>
   </si>
   <si>
     <t>Version</t>
@@ -1204,7 +1252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1217,7 +1265,7 @@
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
+    <col min="13" max="13" width="29" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
     <col min="15" max="15" width="21" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
@@ -1955,7 +2003,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
         <v>66</v>
@@ -1967,43 +2015,43 @@
         <v>21</v>
       </c>
       <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" t="s">
         <v>83</v>
       </c>
-      <c r="F14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>84</v>
       </c>
-      <c r="H14" t="s">
-        <v>85</v>
-      </c>
       <c r="I14" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="J14" t="s">
         <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="L14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O14" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="P14" t="s">
         <v>31</v>
       </c>
       <c r="Q14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="R14" t="s">
         <v>33</v>
@@ -2017,25 +2065,25 @@
         <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s">
         <v>90</v>
       </c>
       <c r="I15" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J15" t="s">
         <v>26</v>
@@ -2044,22 +2092,22 @@
         <v>27</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N15" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O15" t="s">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="P15" t="s">
         <v>31</v>
       </c>
       <c r="Q15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="R15" t="s">
         <v>33</v>
@@ -2070,10 +2118,10 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
         <v>21</v>
@@ -2085,13 +2133,13 @@
         <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s">
         <v>26</v>
@@ -2100,13 +2148,13 @@
         <v>27</v>
       </c>
       <c r="L16">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N16" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="O16" t="s">
         <v>30</v>
@@ -2126,13 +2174,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
@@ -2144,7 +2192,7 @@
         <v>23</v>
       </c>
       <c r="H17" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="I17" t="s">
         <v>62</v>
@@ -2159,10 +2207,10 @@
         <v>65</v>
       </c>
       <c r="M17" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N17" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="O17" t="s">
         <v>30</v>
@@ -2171,7 +2219,7 @@
         <v>31</v>
       </c>
       <c r="Q17" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="R17" t="s">
         <v>33</v>
@@ -2182,13 +2230,13 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
         <v>22</v>
@@ -2200,10 +2248,10 @@
         <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="I18" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="J18" t="s">
         <v>26</v>
@@ -2215,7 +2263,7 @@
         <v>65</v>
       </c>
       <c r="M18" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N18" t="s">
         <v>101</v>
@@ -2227,7 +2275,7 @@
         <v>31</v>
       </c>
       <c r="Q18" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="R18" t="s">
         <v>33</v>
@@ -2238,13 +2286,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" t="s">
         <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>21</v>
       </c>
       <c r="E19" t="s">
         <v>22</v>
@@ -2253,13 +2301,13 @@
         <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H19" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="I19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J19" t="s">
         <v>26</v>
@@ -2268,10 +2316,10 @@
         <v>27</v>
       </c>
       <c r="L19">
+        <v>65</v>
+      </c>
+      <c r="M19" t="s">
         <v>100</v>
-      </c>
-      <c r="M19" t="s">
-        <v>105</v>
       </c>
       <c r="N19" t="s">
         <v>106</v>
@@ -2283,7 +2331,7 @@
         <v>31</v>
       </c>
       <c r="Q19" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="R19" t="s">
         <v>33</v>
@@ -2291,13 +2339,13 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
         <v>21</v>
@@ -2315,22 +2363,22 @@
         <v>68</v>
       </c>
       <c r="I20" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J20" t="s">
         <v>26</v>
       </c>
       <c r="K20" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="L20">
         <v>100</v>
       </c>
       <c r="M20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N20" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="O20" t="s">
         <v>30</v>
@@ -2347,13 +2395,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
         <v>21</v>
@@ -2368,25 +2416,25 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="I21" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J21" t="s">
         <v>26</v>
       </c>
       <c r="K21" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="L21">
         <v>100</v>
       </c>
       <c r="M21" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N21" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="O21" t="s">
         <v>30</v>
@@ -2395,9 +2443,121 @@
         <v>31</v>
       </c>
       <c r="Q21" t="s">
+        <v>33</v>
+      </c>
+      <c r="R21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" t="s">
+        <v>115</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" t="s">
+        <v>109</v>
+      </c>
+      <c r="J22" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" t="s">
+        <v>76</v>
+      </c>
+      <c r="L22">
+        <v>65</v>
+      </c>
+      <c r="M22" t="s">
+        <v>116</v>
+      </c>
+      <c r="N22" t="s">
         <v>111</v>
       </c>
-      <c r="R21" t="s">
+      <c r="O22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>117</v>
+      </c>
+      <c r="R22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" t="s">
+        <v>109</v>
+      </c>
+      <c r="J23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" t="s">
+        <v>27</v>
+      </c>
+      <c r="L23">
+        <v>100</v>
+      </c>
+      <c r="M23" t="s">
+        <v>119</v>
+      </c>
+      <c r="N23" t="s">
+        <v>111</v>
+      </c>
+      <c r="O23" t="s">
+        <v>30</v>
+      </c>
+      <c r="P23" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>120</v>
+      </c>
+      <c r="R23" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2409,7 +2569,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -2426,7 +2586,7 @@
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="28" customWidth="1"/>
+    <col min="17" max="17" width="29" customWidth="1"/>
     <col min="18" max="18" width="21" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="7" customWidth="1"/>
@@ -2438,13 +2598,13 @@
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -2468,22 +2628,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -2492,10 +2652,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -2504,21 +2664,21 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
@@ -2551,7 +2711,7 @@
         <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="O2">
         <v>100</v>
@@ -2586,13 +2746,13 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -2625,7 +2785,7 @@
         <v>23</v>
       </c>
       <c r="N3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="O3">
         <v>65</v>
@@ -2660,13 +2820,13 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
         <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -2675,16 +2835,16 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H4" t="s">
         <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -2699,16 +2859,16 @@
         <v>35</v>
       </c>
       <c r="N4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="Q4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="R4" t="s">
         <v>30</v>
@@ -2734,13 +2894,13 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
@@ -2773,7 +2933,7 @@
         <v>23</v>
       </c>
       <c r="N5" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="O5">
         <v>65</v>
@@ -2808,13 +2968,13 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -2847,7 +3007,7 @@
         <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="O6">
         <v>65</v>
@@ -2882,13 +3042,13 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -2921,7 +3081,7 @@
         <v>35</v>
       </c>
       <c r="N7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -2956,13 +3116,13 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -2971,16 +3131,16 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H8" t="s">
         <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2995,16 +3155,16 @@
         <v>35</v>
       </c>
       <c r="N8" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="Q8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="R8" t="s">
         <v>30</v>
@@ -3019,7 +3179,7 @@
         <v>31</v>
       </c>
       <c r="V8" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="W8" t="s">
         <v>33</v>
@@ -3030,13 +3190,13 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -3069,7 +3229,7 @@
         <v>23</v>
       </c>
       <c r="N9" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="O9">
         <v>65</v>
@@ -3104,13 +3264,13 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -3143,7 +3303,7 @@
         <v>23</v>
       </c>
       <c r="N10" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="O10">
         <v>65</v>
@@ -3178,13 +3338,13 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -3217,7 +3377,7 @@
         <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="O11">
         <v>60</v>
@@ -3252,13 +3412,13 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -3291,7 +3451,7 @@
         <v>23</v>
       </c>
       <c r="N12" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="O12">
         <v>65</v>
@@ -3326,13 +3486,13 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -3365,7 +3525,7 @@
         <v>35</v>
       </c>
       <c r="N13" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -3374,7 +3534,7 @@
         <v>80</v>
       </c>
       <c r="Q13" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="R13" t="s">
         <v>30</v>
@@ -3389,7 +3549,7 @@
         <v>31</v>
       </c>
       <c r="V13" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="W13" t="s">
         <v>33</v>
@@ -3400,13 +3560,13 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -3418,7 +3578,7 @@
         <v>66</v>
       </c>
       <c r="G14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s">
         <v>21</v>
@@ -3436,22 +3596,22 @@
         <v>33</v>
       </c>
       <c r="M14" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="N14" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="O14">
         <v>50</v>
       </c>
       <c r="P14" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="Q14" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="R14" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -3463,7 +3623,7 @@
         <v>31</v>
       </c>
       <c r="V14" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="W14" t="s">
         <v>33</v>
@@ -3474,13 +3634,13 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -3489,16 +3649,16 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G15" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H15" t="s">
         <v>21</v>
       </c>
       <c r="I15" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -3513,7 +3673,7 @@
         <v>23</v>
       </c>
       <c r="N15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="O15">
         <v>65</v>
@@ -3522,7 +3682,7 @@
         <v>62</v>
       </c>
       <c r="Q15" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R15" t="s">
         <v>30</v>
@@ -3537,7 +3697,7 @@
         <v>31</v>
       </c>
       <c r="V15" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="W15" t="s">
         <v>33</v>
@@ -3548,13 +3708,13 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -3563,16 +3723,16 @@
         <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G16" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H16" t="s">
         <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -3587,7 +3747,7 @@
         <v>23</v>
       </c>
       <c r="N16" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="O16">
         <v>65</v>
@@ -3596,7 +3756,7 @@
         <v>62</v>
       </c>
       <c r="Q16" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R16" t="s">
         <v>30</v>
@@ -3622,13 +3782,13 @@
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -3637,16 +3797,16 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I17" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -3661,16 +3821,16 @@
         <v>23</v>
       </c>
       <c r="N17" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="O17">
         <v>65</v>
       </c>
       <c r="P17" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q17" t="s">
         <v>100</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>95</v>
       </c>
       <c r="R17" t="s">
         <v>30</v>
@@ -3685,7 +3845,7 @@
         <v>31</v>
       </c>
       <c r="V17" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="W17" t="s">
         <v>33</v>
@@ -3696,13 +3856,13 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -3735,7 +3895,7 @@
         <v>23</v>
       </c>
       <c r="N18" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="O18">
         <v>65</v>
@@ -3770,13 +3930,13 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -3809,7 +3969,7 @@
         <v>35</v>
       </c>
       <c r="N19" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -3844,13 +4004,13 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D20" t="s">
         <v>74</v>
@@ -3883,7 +4043,7 @@
         <v>35</v>
       </c>
       <c r="N20" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -3918,13 +4078,13 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D21" t="s">
         <v>74</v>
@@ -3933,16 +4093,16 @@
         <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G21" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H21" t="s">
         <v>21</v>
       </c>
       <c r="I21" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -3957,16 +4117,16 @@
         <v>35</v>
       </c>
       <c r="N21" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="Q21" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="R21" t="s">
         <v>30</v>
@@ -3987,6 +4147,154 @@
         <v>33</v>
       </c>
       <c r="X21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>165</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22" t="s">
+        <v>33</v>
+      </c>
+      <c r="M22" t="s">
+        <v>83</v>
+      </c>
+      <c r="N22" t="s">
+        <v>152</v>
+      </c>
+      <c r="O22">
+        <v>100</v>
+      </c>
+      <c r="P22" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>85</v>
+      </c>
+      <c r="R22" t="s">
+        <v>30</v>
+      </c>
+      <c r="S22" t="s">
+        <v>33</v>
+      </c>
+      <c r="T22" t="s">
+        <v>33</v>
+      </c>
+      <c r="U22" t="s">
+        <v>31</v>
+      </c>
+      <c r="V22" t="s">
+        <v>86</v>
+      </c>
+      <c r="W22" t="s">
+        <v>33</v>
+      </c>
+      <c r="X22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>166</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" t="s">
+        <v>111</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+      <c r="L23" t="s">
+        <v>33</v>
+      </c>
+      <c r="M23" t="s">
+        <v>115</v>
+      </c>
+      <c r="N23" t="s">
+        <v>140</v>
+      </c>
+      <c r="O23">
+        <v>65</v>
+      </c>
+      <c r="P23" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>116</v>
+      </c>
+      <c r="R23" t="s">
+        <v>30</v>
+      </c>
+      <c r="S23" t="s">
+        <v>33</v>
+      </c>
+      <c r="T23" t="s">
+        <v>33</v>
+      </c>
+      <c r="U23" t="s">
+        <v>31</v>
+      </c>
+      <c r="V23" t="s">
+        <v>117</v>
+      </c>
+      <c r="W23" t="s">
+        <v>33</v>
+      </c>
+      <c r="X23" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4008,7 +4316,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4035,19 +4343,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -4061,7 +4369,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -4082,61 +4390,61 @@
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>16</v>
@@ -4144,13 +4452,13 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -4201,18 +4509,18 @@
         <v>33</v>
       </c>
       <c r="T2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -4268,13 +4576,13 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -4330,13 +4638,13 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C5" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -4345,10 +4653,10 @@
         <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G5" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H5" t="s">
         <v>33</v>
@@ -4387,18 +4695,18 @@
         <v>33</v>
       </c>
       <c r="T5" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C6" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -4407,10 +4715,10 @@
         <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G6" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H6" t="s">
         <v>33</v>
@@ -4454,13 +4762,13 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C7" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -4469,10 +4777,10 @@
         <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G7" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H7" t="s">
         <v>33</v>
@@ -4516,13 +4824,13 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B8" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C8" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -4531,10 +4839,10 @@
         <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G8" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="H8" t="s">
         <v>33</v>
@@ -4573,18 +4881,18 @@
         <v>33</v>
       </c>
       <c r="T8" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -4593,10 +4901,10 @@
         <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G9" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="H9" t="s">
         <v>33</v>
@@ -4640,13 +4948,13 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -4655,10 +4963,10 @@
         <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G10" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="H10" t="s">
         <v>33</v>
@@ -4702,13 +5010,13 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B11" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C11" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -4741,36 +5049,36 @@
         <v>33</v>
       </c>
       <c r="N11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="O11" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="P11" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q11" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="R11" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="S11" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="T11" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -4803,22 +5111,22 @@
         <v>33</v>
       </c>
       <c r="N12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="O12" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="P12" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q12" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="R12" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="S12" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="T12" t="s">
         <v>33</v>
@@ -4826,13 +5134,13 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B13" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="D13" t="s">
         <v>33</v>
@@ -4865,22 +5173,22 @@
         <v>33</v>
       </c>
       <c r="N13" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="O13" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="P13" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q13" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="R13" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="S13" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="T13" t="s">
         <v>33</v>
@@ -4888,10 +5196,10 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B14" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
@@ -4930,33 +5238,33 @@
         <v>33</v>
       </c>
       <c r="O14" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="P14" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Q14" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="R14" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="S14" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="T14" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B15" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C15" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="D15" t="s">
         <v>33</v>
@@ -4965,7 +5273,7 @@
         <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
         <v>33</v>
@@ -4992,30 +5300,30 @@
         <v>33</v>
       </c>
       <c r="O15" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="P15" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="Q15" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="R15" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="S15" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="T15" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C16" t="s">
         <v>33</v>
@@ -5027,16 +5335,16 @@
         <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G16" t="s">
         <v>33</v>
       </c>
       <c r="H16" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="I16" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="J16" t="s">
         <v>33</v>
@@ -5074,10 +5382,10 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -5086,19 +5394,19 @@
         <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F17" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G17" t="s">
         <v>33</v>
       </c>
       <c r="H17" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="I17" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="J17" t="s">
         <v>33</v>
@@ -5136,13 +5444,13 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B18" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C18" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D18" t="s">
         <v>33</v>
@@ -5193,15 +5501,15 @@
         <v>33</v>
       </c>
       <c r="T18" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
@@ -5225,19 +5533,19 @@
         <v>33</v>
       </c>
       <c r="J19" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="K19" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L19" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M19" t="s">
         <v>33</v>
       </c>
       <c r="N19" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="O19" t="s">
         <v>33</v>
@@ -5260,13 +5568,13 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C20" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="D20" t="s">
         <v>33</v>
@@ -5317,15 +5625,15 @@
         <v>33</v>
       </c>
       <c r="T20" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -5349,13 +5657,13 @@
         <v>33</v>
       </c>
       <c r="J21" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="K21" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="L21" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="M21" t="s">
         <v>33</v>
@@ -5380,6 +5688,68 @@
       </c>
       <c r="T21" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>238</v>
+      </c>
+      <c r="B22" t="s">
+        <v>239</v>
+      </c>
+      <c r="C22" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" t="s">
+        <v>33</v>
+      </c>
+      <c r="J22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" t="s">
+        <v>33</v>
+      </c>
+      <c r="M22" t="s">
+        <v>33</v>
+      </c>
+      <c r="N22" t="s">
+        <v>33</v>
+      </c>
+      <c r="O22" t="s">
+        <v>33</v>
+      </c>
+      <c r="P22" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>33</v>
+      </c>
+      <c r="R22" t="s">
+        <v>33</v>
+      </c>
+      <c r="S22" t="s">
+        <v>33</v>
+      </c>
+      <c r="T22" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -5401,27 +5771,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -5441,7 +5811,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
@@ -5461,10 +5831,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
@@ -5481,10 +5851,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
@@ -5501,10 +5871,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B6" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
@@ -5527,7 +5897,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -5544,10 +5914,10 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="C8" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -5567,7 +5937,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -5584,10 +5954,10 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="C10" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -5601,13 +5971,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -5621,13 +5991,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="B12" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -5641,13 +6011,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="B13" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="D13" t="s">
         <v>33</v>
@@ -5661,13 +6031,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
         <v>33</v>
@@ -5681,13 +6051,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D15" t="s">
         <v>33</v>
@@ -5701,13 +6071,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="D16" t="s">
         <v>33</v>
@@ -5721,13 +6091,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="B17" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C17" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="D17" t="s">
         <v>33</v>
@@ -5741,16 +6111,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="D18" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5767,7 +6137,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -5776,39 +6146,39 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="B3" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
@@ -5816,7 +6186,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -5824,23 +6194,23 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="B7" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="B8" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
@@ -5848,9 +6218,17 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="B10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>284</v>
+      </c>
+      <c r="B11" t="s">
         <v>33</v>
       </c>
     </row>

--- a/apps/web/public/examples/example-with-constraint-rules.xlsx
+++ b/apps/web/public/examples/example-with-constraint-rules.xlsx
@@ -76,10 +76,10 @@
     <t>FA</t>
   </si>
   <si>
-    <t>CORE</t>
-  </si>
-  <si>
-    <t>100</t>
+    <t>AMUS</t>
+  </si>
+  <si>
+    <t>228</t>
   </si>
   <si>
     <t>A</t>
@@ -88,300 +88,300 @@
     <t>4</t>
   </si>
   <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>10:20:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>NH 103</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>FA-Full</t>
+  </si>
+  <si>
+    <t>Harmonic Structures</t>
+  </si>
+  <si>
+    <t>Ada Example</t>
+  </si>
+  <si>
+    <t>Lecture</t>
+  </si>
+  <si>
+    <t>In-Person</t>
+  </si>
+  <si>
+    <t>Cohort course: clashes with BHAV 212 A</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>MWF</t>
   </si>
   <si>
+    <t>11:00:00 - 12:05:00</t>
+  </si>
+  <si>
+    <t>The second section is what lets the cohort rule be met</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>SP-Full</t>
+  </si>
+  <si>
+    <t>Multivoice Analysis</t>
+  </si>
+  <si>
+    <t>Cy Fictional</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>15:05:00 - 15:55:00</t>
+  </si>
+  <si>
+    <t>NH 276</t>
+  </si>
+  <si>
+    <t>Colloquium</t>
+  </si>
+  <si>
+    <t>Seminar</t>
+  </si>
+  <si>
+    <t>Not a standard time; allowed by this department's rule</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
     <t>09:15:00 - 10:20:00</t>
   </si>
   <si>
+    <t>NH 104</t>
+  </si>
+  <si>
+    <t>Discrete Rhythm</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:40:00</t>
+  </si>
+  <si>
+    <t>Introductory Harmonic Structures</t>
+  </si>
+  <si>
+    <t>Tuesday only: some of the days of TR at 8:00; allowed by this department's subset rule</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>14:10:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>Corpus Studies I</t>
+  </si>
+  <si>
+    <t>Ben Sample</t>
+  </si>
+  <si>
+    <t>Runs into the colloquium hour (R 15:05)</t>
+  </si>
+  <si>
+    <t>BHAV</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>NH 106</t>
+  </si>
+  <si>
+    <t>Introduction to Behavioral Dynamics</t>
+  </si>
+  <si>
+    <t>Lee</t>
+  </si>
+  <si>
+    <t>Lee's two sections are not back to back</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>10:30:00 - 11:35:00</t>
+  </si>
+  <si>
+    <t>NH 107</t>
+  </si>
+  <si>
+    <t>Dee Placeholder</t>
+  </si>
+  <si>
+    <t>10:30 is not a standard start (shown in orange)</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>NH 105</t>
+  </si>
+  <si>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>Eli Specimen</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Applied Field Analysis</t>
+  </si>
+  <si>
+    <t>Friday only: some of the days of MWF at 9:15; not covered by the subset rule</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:55:00</t>
+  </si>
+  <si>
+    <t>Stochastic Behavior</t>
+  </si>
+  <si>
+    <t>Same time as DIGI 318 A</t>
+  </si>
+  <si>
+    <t>CRUD</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>14:45:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>SB 120</t>
+  </si>
+  <si>
+    <t>Introduction to Urban Systems</t>
+  </si>
+  <si>
+    <t>Kim</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:05:00</t>
+  </si>
+  <si>
+    <t>SB 121</t>
+  </si>
+  <si>
+    <t>Gus Testwell</t>
+  </si>
+  <si>
+    <t>8:00 MWF is standard for the university but disallowed by this department's rule</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>13:30:00 - 14:35:00</t>
+  </si>
+  <si>
+    <t>Urban Data Structures</t>
+  </si>
+  <si>
+    <t>Kim teaches three in a row on MWF</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>16:00:00 - 17:00:00</t>
+  </si>
+  <si>
+    <t>SB 122</t>
+  </si>
+  <si>
+    <t>Planning Algorithms</t>
+  </si>
+  <si>
+    <t>DIGI</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>SB 110</t>
+  </si>
+  <si>
+    <t>Information Computing</t>
+  </si>
+  <si>
+    <t>Fay Mockson</t>
+  </si>
+  <si>
+    <t>Digital Information Topics</t>
+  </si>
+  <si>
+    <t>Same time as BHAV 312 A</t>
+  </si>
+  <si>
+    <t>HELP</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>HH 210</t>
   </si>
   <si>
-    <t>Full</t>
-  </si>
-  <si>
-    <t>FA-Full</t>
-  </si>
-  <si>
-    <t>Core 100</t>
+    <t>Ecology Core</t>
   </si>
   <si>
     <t>Hal Fakename</t>
   </si>
   <si>
-    <t>Lecture</t>
-  </si>
-  <si>
-    <t>In-Person</t>
-  </si>
-  <si>
     <t>There is no evening section yet</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:55:00</t>
-  </si>
-  <si>
-    <t>CS</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>14:45:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>SB 120</t>
-  </si>
-  <si>
-    <t>Introduction to Computing</t>
-  </si>
-  <si>
-    <t>Kim</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:05:00</t>
-  </si>
-  <si>
-    <t>SB 121</t>
-  </si>
-  <si>
-    <t>Gus Testwell</t>
-  </si>
-  <si>
-    <t>8:00 MWF is standard for the university but disallowed by this department's rule</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>13:30:00 - 14:35:00</t>
-  </si>
-  <si>
-    <t>Data Structures</t>
-  </si>
-  <si>
-    <t>Kim teaches three in a row on MWF</t>
-  </si>
-  <si>
-    <t>372</t>
-  </si>
-  <si>
-    <t>16:00:00 - 17:00:00</t>
-  </si>
-  <si>
-    <t>SB 122</t>
-  </si>
-  <si>
-    <t>Algorithms</t>
-  </si>
-  <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>11:00:00 - 12:05:00</t>
-  </si>
-  <si>
-    <t>SB 110</t>
-  </si>
-  <si>
-    <t>Data Computing</t>
-  </si>
-  <si>
-    <t>Fay Mockson</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>NH 106</t>
-  </si>
-  <si>
-    <t>Data Science Topics</t>
-  </si>
-  <si>
-    <t>Ben Sample</t>
-  </si>
-  <si>
-    <t>Same time as STAT 343 A</t>
-  </si>
-  <si>
-    <t>MATH</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>10:20:00 - 12:00:00</t>
-  </si>
-  <si>
-    <t>NH 103</t>
-  </si>
-  <si>
-    <t>Linear Algebra</t>
-  </si>
-  <si>
-    <t>Ada Example</t>
-  </si>
-  <si>
-    <t>Cohort course: clashes with STAT 243 A</t>
-  </si>
-  <si>
-    <t>The second section is what lets the cohort rule be met</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>SP-Full</t>
-  </si>
-  <si>
-    <t>Multivariable Calculus</t>
-  </si>
-  <si>
-    <t>Cy Fictional</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>NH 104</t>
-  </si>
-  <si>
-    <t>Discrete Mathematics</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:40:00</t>
-  </si>
-  <si>
-    <t>Introductory Linear Algebra</t>
-  </si>
-  <si>
-    <t>Tuesday only: some of the days of TR at 8:00; allowed by this department's subset rule</t>
-  </si>
-  <si>
-    <t>290</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>15:05:00 - 15:55:00</t>
-  </si>
-  <si>
-    <t>NH 276</t>
-  </si>
-  <si>
-    <t>Colloquium</t>
-  </si>
-  <si>
-    <t>Seminar</t>
-  </si>
-  <si>
-    <t>Not a standard time; allowed by this department's rule</t>
-  </si>
-  <si>
-    <t>14:10:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>Real Analysis I</t>
-  </si>
-  <si>
-    <t>Runs into the colloquium hour (R 15:05)</t>
-  </si>
-  <si>
-    <t>STAT</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>Introduction to Statistics</t>
-  </si>
-  <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>Lee's two sections are not back to back</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>10:30:00 - 11:35:00</t>
-  </si>
-  <si>
-    <t>NH 107</t>
-  </si>
-  <si>
-    <t>Dee Placeholder</t>
-  </si>
-  <si>
-    <t>10:30 is not a standard start (shown in orange)</t>
-  </si>
-  <si>
-    <t>243</t>
-  </si>
-  <si>
-    <t>NH 105</t>
-  </si>
-  <si>
-    <t>Statistical Methods</t>
-  </si>
-  <si>
-    <t>Eli Specimen</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>Regression Models</t>
-  </si>
-  <si>
-    <t>245</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Applied Data Analysis</t>
-  </si>
-  <si>
-    <t>Friday only: some of the days of MWF at 9:15; not covered by the subset rule</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>Same time as DATA 301 A</t>
-  </si>
-  <si>
     <t>SectionId</t>
   </si>
   <si>
@@ -418,7 +418,7 @@
     <t>EnrollmentDay10</t>
   </si>
   <si>
-    <t>AY25-FA-MATH231-A</t>
+    <t>AY25-FA-AMUS228-A</t>
   </si>
   <si>
     <t>AY25</t>
@@ -427,97 +427,97 @@
     <t>10:20</t>
   </si>
   <si>
-    <t>AY25-FA-MATH231-B</t>
+    <t>AY25-FA-AMUS228-B</t>
   </si>
   <si>
     <t>11:00</t>
   </si>
   <si>
-    <t>AY25-FA-STAT243-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-MATH250-A</t>
+    <t>AY25-FA-BHAV212-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS261-A</t>
   </si>
   <si>
     <t>09:15</t>
   </si>
   <si>
-    <t>AY25-FA-DATA202-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DATA301-A</t>
+    <t>AY25-FA-DIGI225-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI318-A</t>
   </si>
   <si>
     <t>12:15</t>
   </si>
   <si>
-    <t>AY25-FA-STAT343-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-CS262-A</t>
+    <t>AY25-FA-BHAV312-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-CRUD245-A</t>
   </si>
   <si>
     <t>13:30</t>
   </si>
   <si>
-    <t>AY25-FA-CS108-A</t>
+    <t>AY25-FA-CRUD167-A</t>
   </si>
   <si>
     <t>14:45</t>
   </si>
   <si>
-    <t>AY25-FA-CS372-A</t>
+    <t>AY25-FA-CRUD315-A</t>
   </si>
   <si>
     <t>16:00</t>
   </si>
   <si>
-    <t>AY25-FA-CS108-B</t>
+    <t>AY25-FA-CRUD167-B</t>
   </si>
   <si>
     <t>08:00</t>
   </si>
   <si>
-    <t>AY25-FA-MATH301-A</t>
+    <t>AY25-FA-AMUS318-A</t>
   </si>
   <si>
     <t>14:10</t>
   </si>
   <si>
-    <t>AY25-FA-MATH290-A</t>
+    <t>AY25-FA-AMUS241-A</t>
   </si>
   <si>
     <t>15:05</t>
   </si>
   <si>
-    <t>AY25-FA-STAT143-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-STAT143-B</t>
-  </si>
-  <si>
-    <t>AY25-FA-STAT143-C</t>
+    <t>AY25-FA-BHAV112-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV112-B</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV112-C</t>
   </si>
   <si>
     <t>10:30</t>
   </si>
   <si>
-    <t>AY25-FA-CORE100-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-CORE100-B</t>
-  </si>
-  <si>
-    <t>AY25-SP-MATH232-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-STAT244-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-MATH255-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-STAT245-A</t>
+    <t>AY25-FA-HELP111-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-HELP111-B</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS235-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV219-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS296-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV226-A</t>
   </si>
   <si>
     <t>Activity</t>
@@ -574,28 +574,28 @@
     <t>Meets</t>
   </si>
   <si>
-    <t>Math major, year 2</t>
+    <t>AMUS major, year 2</t>
   </si>
   <si>
     <t>takeable</t>
   </si>
   <si>
-    <t>MATH 231</t>
-  </si>
-  <si>
-    <t>A cohort that must be able to take all three courses together. MATH 231 has two sections so this is met.</t>
-  </si>
-  <si>
-    <t>STAT 243</t>
-  </si>
-  <si>
-    <t>MATH 250</t>
-  </si>
-  <si>
-    <t>Data science minor: any two electives</t>
-  </si>
-  <si>
-    <t>DATA 301</t>
+    <t>AMUS 228</t>
+  </si>
+  <si>
+    <t>A cohort that must be able to take all three courses together. AMUS 228 has two sections so this is met.</t>
+  </si>
+  <si>
+    <t>BHAV 212</t>
+  </si>
+  <si>
+    <t>AMUS 261</t>
+  </si>
+  <si>
+    <t>Digital information minor: any two electives</t>
+  </si>
+  <si>
+    <t>DIGI 318</t>
   </si>
   <si>
     <t>2</t>
@@ -604,16 +604,16 @@
     <t>any</t>
   </si>
   <si>
-    <t>Any two of the three should fit together. DATA 301 and STAT 343 clash.</t>
-  </si>
-  <si>
-    <t>STAT 343</t>
-  </si>
-  <si>
-    <t>CS 262</t>
-  </si>
-  <si>
-    <t>Data science minor: some pair of electives</t>
+    <t>Any two of the three should fit together. DIGI 318 and BHAV 312 clash.</t>
+  </si>
+  <si>
+    <t>BHAV 312</t>
+  </si>
+  <si>
+    <t>CRUD 245</t>
+  </si>
+  <si>
+    <t>Digital information minor: some pair of electives</t>
   </si>
   <si>
     <t>some</t>
@@ -628,7 +628,7 @@
     <t>window</t>
   </si>
   <si>
-    <t>MATH 3*</t>
+    <t>AMUS 3*</t>
   </si>
   <si>
     <t>15:55</t>
@@ -643,10 +643,10 @@
     <t>No 300-level class during the colloquium.</t>
   </si>
   <si>
-    <t>STAT 3*</t>
-  </si>
-  <si>
-    <t>DATA 3*</t>
+    <t>BHAV 3*</t>
+  </si>
+  <si>
+    <t>DIGI 3*</t>
   </si>
   <si>
     <t>Gus does not teach before 9:00</t>
@@ -661,10 +661,10 @@
     <t>A rule about an instructor instead of courses.</t>
   </si>
   <si>
-    <t>Core 100 needs an evening section</t>
-  </si>
-  <si>
-    <t>CORE 100</t>
+    <t>Ecology Core needs an evening section</t>
+  </si>
+  <si>
+    <t>HELP 111</t>
   </si>
   <si>
     <t>17:00</t>
@@ -706,7 +706,7 @@
     <t>standard</t>
   </si>
   <si>
-    <t>MATH 290</t>
+    <t>AMUS 241</t>
   </si>
   <si>
     <t>The colloquium meets at a time that is not standard.</t>
@@ -733,16 +733,16 @@
     <t>65</t>
   </si>
   <si>
-    <t>Linear algebra may meet one day of TR</t>
+    <t>Harmonic structures may meet one day of TR</t>
   </si>
   <si>
     <t>subset</t>
   </si>
   <si>
-    <t>MATH 255</t>
-  </si>
-  <si>
-    <t>MATH 255 is meant to meet on only one of the standard days, so it is not flagged for that.</t>
+    <t>AMUS 296</t>
+  </si>
+  <si>
+    <t>AMUS 296 is meant to meet on only one of the standard days, so it is not flagged for that.</t>
   </si>
   <si>
     <t>Kind</t>
@@ -838,13 +838,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-03</t>
+    <t>2026-10-04</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>22:57:57</t>
+    <t>08:26:04</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -1265,7 +1265,7 @@
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="29" customWidth="1"/>
+    <col min="13" max="13" width="37" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
     <col min="15" max="15" width="21" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
@@ -1364,7 +1364,7 @@
         <v>27</v>
       </c>
       <c r="L2">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M2" t="s">
         <v>28</v>
@@ -1420,7 +1420,7 @@
         <v>27</v>
       </c>
       <c r="L3">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M3" t="s">
         <v>28</v>
@@ -1435,7 +1435,7 @@
         <v>31</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="R3" t="s">
         <v>33</v>
@@ -1443,13 +1443,13 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -1464,19 +1464,19 @@
         <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
         <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="L4">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s">
         <v>41</v>
@@ -1502,28 +1502,28 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s">
         <v>26</v>
@@ -1532,22 +1532,22 @@
         <v>27</v>
       </c>
       <c r="L5">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="P5" t="s">
         <v>31</v>
       </c>
       <c r="Q5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="R5" t="s">
         <v>33</v>
@@ -1558,10 +1558,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
         <v>21</v>
@@ -1573,13 +1573,13 @@
         <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J6" t="s">
         <v>26</v>
@@ -1591,7 +1591,7 @@
         <v>65</v>
       </c>
       <c r="M6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="N6" t="s">
         <v>42</v>
@@ -1603,7 +1603,7 @@
         <v>31</v>
       </c>
       <c r="Q6" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="R6" t="s">
         <v>33</v>
@@ -1611,13 +1611,13 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
         <v>21</v>
@@ -1629,25 +1629,25 @@
         <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="H7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I7" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
         <v>26</v>
       </c>
       <c r="K7" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="L7">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N7" t="s">
         <v>42</v>
@@ -1659,7 +1659,7 @@
         <v>31</v>
       </c>
       <c r="Q7" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="R7" t="s">
         <v>33</v>
@@ -1670,10 +1670,10 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
         <v>21</v>
@@ -1688,10 +1688,10 @@
         <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J8" t="s">
         <v>26</v>
@@ -1700,13 +1700,13 @@
         <v>27</v>
       </c>
       <c r="L8">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O8" t="s">
         <v>30</v>
@@ -1715,7 +1715,7 @@
         <v>31</v>
       </c>
       <c r="Q8" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="R8" t="s">
         <v>33</v>
@@ -1726,10 +1726,10 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
@@ -1744,10 +1744,10 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J9" t="s">
         <v>26</v>
@@ -1756,13 +1756,13 @@
         <v>27</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O9" t="s">
         <v>30</v>
@@ -1771,7 +1771,7 @@
         <v>31</v>
       </c>
       <c r="Q9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="R9" t="s">
         <v>33</v>
@@ -1782,13 +1782,13 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
         <v>66</v>
       </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
@@ -1800,10 +1800,10 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J10" t="s">
         <v>26</v>
@@ -1812,13 +1812,13 @@
         <v>27</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O10" t="s">
         <v>30</v>
@@ -1827,7 +1827,7 @@
         <v>31</v>
       </c>
       <c r="Q10" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="R10" t="s">
         <v>33</v>
@@ -1838,13 +1838,13 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
         <v>66</v>
       </c>
-      <c r="C11" t="s">
-        <v>67</v>
-      </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
@@ -1853,13 +1853,13 @@
         <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
         <v>26</v>
@@ -1871,10 +1871,10 @@
         <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O11" t="s">
         <v>30</v>
@@ -1883,7 +1883,7 @@
         <v>31</v>
       </c>
       <c r="Q11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="R11" t="s">
         <v>33</v>
@@ -1891,13 +1891,13 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
@@ -1909,28 +1909,28 @@
         <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J12" t="s">
         <v>26</v>
       </c>
       <c r="K12" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O12" t="s">
         <v>30</v>
@@ -1947,13 +1947,13 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
         <v>21</v>
@@ -1971,22 +1971,22 @@
         <v>24</v>
       </c>
       <c r="I13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s">
         <v>26</v>
       </c>
       <c r="K13" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="L13">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M13" t="s">
         <v>81</v>
       </c>
       <c r="N13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O13" t="s">
         <v>30</v>
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
         <v>82</v>
@@ -2024,25 +2024,25 @@
         <v>83</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="I14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s">
         <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O14" t="s">
         <v>30</v>
@@ -2051,7 +2051,7 @@
         <v>31</v>
       </c>
       <c r="Q14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R14" t="s">
         <v>33</v>
@@ -2062,28 +2062,28 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="H15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I15" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s">
         <v>26</v>
@@ -2092,22 +2092,22 @@
         <v>27</v>
       </c>
       <c r="L15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N15" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="O15" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="P15" t="s">
         <v>31</v>
       </c>
       <c r="Q15" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="R15" t="s">
         <v>33</v>
@@ -2118,10 +2118,10 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>21</v>
@@ -2136,10 +2136,10 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J16" t="s">
         <v>26</v>
@@ -2148,13 +2148,13 @@
         <v>27</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N16" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="O16" t="s">
         <v>30</v>
@@ -2163,7 +2163,7 @@
         <v>31</v>
       </c>
       <c r="Q16" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="R16" t="s">
         <v>33</v>
@@ -2174,13 +2174,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
@@ -2189,13 +2189,13 @@
         <v>22</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="J17" t="s">
         <v>26</v>
@@ -2207,10 +2207,10 @@
         <v>65</v>
       </c>
       <c r="M17" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O17" t="s">
         <v>30</v>
@@ -2219,7 +2219,7 @@
         <v>31</v>
       </c>
       <c r="Q17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="R17" t="s">
         <v>33</v>
@@ -2230,13 +2230,13 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
         <v>22</v>
@@ -2245,13 +2245,13 @@
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="I18" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="J18" t="s">
         <v>26</v>
@@ -2263,10 +2263,10 @@
         <v>65</v>
       </c>
       <c r="M18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N18" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O18" t="s">
         <v>30</v>
@@ -2275,7 +2275,7 @@
         <v>31</v>
       </c>
       <c r="Q18" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="R18" t="s">
         <v>33</v>
@@ -2286,13 +2286,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
         <v>22</v>
@@ -2301,13 +2301,13 @@
         <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J19" t="s">
         <v>26</v>
@@ -2316,13 +2316,13 @@
         <v>27</v>
       </c>
       <c r="L19">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M19" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="N19" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="O19" t="s">
         <v>30</v>
@@ -2331,7 +2331,7 @@
         <v>31</v>
       </c>
       <c r="Q19" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="R19" t="s">
         <v>33</v>
@@ -2342,10 +2342,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
         <v>21</v>
@@ -2360,10 +2360,10 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J20" t="s">
         <v>26</v>
@@ -2372,13 +2372,13 @@
         <v>27</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O20" t="s">
         <v>30</v>
@@ -2395,13 +2395,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
         <v>21</v>
@@ -2413,19 +2413,19 @@
         <v>22</v>
       </c>
       <c r="G21" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H21" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="J21" t="s">
         <v>26</v>
       </c>
       <c r="K21" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -2434,7 +2434,7 @@
         <v>113</v>
       </c>
       <c r="N21" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="O21" t="s">
         <v>30</v>
@@ -2443,7 +2443,7 @@
         <v>31</v>
       </c>
       <c r="Q21" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="R21" t="s">
         <v>33</v>
@@ -2451,13 +2451,13 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
         <v>21</v>
@@ -2469,28 +2469,28 @@
         <v>22</v>
       </c>
       <c r="G22" t="s">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I22" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J22" t="s">
         <v>26</v>
       </c>
       <c r="K22" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="L22">
         <v>65</v>
       </c>
       <c r="M22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N22" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="O22" t="s">
         <v>30</v>
@@ -2499,7 +2499,7 @@
         <v>31</v>
       </c>
       <c r="Q22" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="R22" t="s">
         <v>33</v>
@@ -2510,13 +2510,13 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
         <v>22</v>
@@ -2525,13 +2525,13 @@
         <v>22</v>
       </c>
       <c r="G23" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I23" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J23" t="s">
         <v>26</v>
@@ -2543,10 +2543,10 @@
         <v>100</v>
       </c>
       <c r="M23" t="s">
+        <v>118</v>
+      </c>
+      <c r="N23" t="s">
         <v>119</v>
-      </c>
-      <c r="N23" t="s">
-        <v>111</v>
       </c>
       <c r="O23" t="s">
         <v>30</v>
@@ -2555,7 +2555,7 @@
         <v>31</v>
       </c>
       <c r="Q23" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="R23" t="s">
         <v>33</v>
@@ -2586,7 +2586,7 @@
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="29" customWidth="1"/>
+    <col min="17" max="17" width="37" customWidth="1"/>
     <col min="18" max="18" width="21" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="7" customWidth="1"/>
@@ -2687,16 +2687,16 @@
         <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -2708,7 +2708,7 @@
         <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N2" t="s">
         <v>135</v>
@@ -2717,10 +2717,10 @@
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="R2" t="s">
         <v>30</v>
@@ -2735,7 +2735,7 @@
         <v>31</v>
       </c>
       <c r="V2" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="W2" t="s">
         <v>33</v>
@@ -2761,16 +2761,16 @@
         <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
         <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -2782,7 +2782,7 @@
         <v>33</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N3" t="s">
         <v>137</v>
@@ -2791,10 +2791,10 @@
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="Q3" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="R3" t="s">
         <v>30</v>
@@ -2809,7 +2809,7 @@
         <v>31</v>
       </c>
       <c r="V3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="W3" t="s">
         <v>33</v>
@@ -2835,16 +2835,16 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="H4" t="s">
         <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -2856,7 +2856,7 @@
         <v>33</v>
       </c>
       <c r="M4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N4" t="s">
         <v>135</v>
@@ -2865,10 +2865,10 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="Q4" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="R4" t="s">
         <v>30</v>
@@ -2909,16 +2909,16 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="H5" t="s">
         <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -2930,7 +2930,7 @@
         <v>33</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N5" t="s">
         <v>140</v>
@@ -2939,10 +2939,10 @@
         <v>65</v>
       </c>
       <c r="P5" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="Q5" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="R5" t="s">
         <v>30</v>
@@ -2983,16 +2983,16 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="G6" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="H6" t="s">
         <v>21</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3004,7 +3004,7 @@
         <v>33</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N6" t="s">
         <v>137</v>
@@ -3013,10 +3013,10 @@
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="Q6" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="R6" t="s">
         <v>30</v>
@@ -3057,16 +3057,16 @@
         <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="G7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
         <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3078,7 +3078,7 @@
         <v>33</v>
       </c>
       <c r="M7" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N7" t="s">
         <v>143</v>
@@ -3087,10 +3087,10 @@
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="Q7" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="R7" t="s">
         <v>30</v>
@@ -3105,7 +3105,7 @@
         <v>31</v>
       </c>
       <c r="V7" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="W7" t="s">
         <v>33</v>
@@ -3131,16 +3131,16 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="H8" t="s">
         <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3152,7 +3152,7 @@
         <v>33</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N8" t="s">
         <v>143</v>
@@ -3161,10 +3161,10 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="Q8" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="R8" t="s">
         <v>30</v>
@@ -3179,7 +3179,7 @@
         <v>31</v>
       </c>
       <c r="V8" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="W8" t="s">
         <v>33</v>
@@ -3205,16 +3205,16 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="H9" t="s">
         <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -3226,7 +3226,7 @@
         <v>33</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N9" t="s">
         <v>146</v>
@@ -3235,10 +3235,10 @@
         <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="Q9" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="R9" t="s">
         <v>30</v>
@@ -3253,7 +3253,7 @@
         <v>31</v>
       </c>
       <c r="V9" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="W9" t="s">
         <v>33</v>
@@ -3279,16 +3279,16 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
         <v>21</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3300,7 +3300,7 @@
         <v>33</v>
       </c>
       <c r="M10" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N10" t="s">
         <v>148</v>
@@ -3309,10 +3309,10 @@
         <v>65</v>
       </c>
       <c r="P10" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="Q10" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="R10" t="s">
         <v>30</v>
@@ -3353,16 +3353,16 @@
         <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="H11" t="s">
         <v>21</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3374,7 +3374,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N11" t="s">
         <v>150</v>
@@ -3383,10 +3383,10 @@
         <v>60</v>
       </c>
       <c r="P11" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="Q11" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="R11" t="s">
         <v>30</v>
@@ -3427,16 +3427,16 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s">
         <v>34</v>
       </c>
       <c r="I12" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -3448,7 +3448,7 @@
         <v>33</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N12" t="s">
         <v>152</v>
@@ -3457,10 +3457,10 @@
         <v>65</v>
       </c>
       <c r="P12" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="Q12" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="R12" t="s">
         <v>30</v>
@@ -3475,7 +3475,7 @@
         <v>31</v>
       </c>
       <c r="V12" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="W12" t="s">
         <v>33</v>
@@ -3501,16 +3501,16 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="G13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
         <v>21</v>
       </c>
       <c r="I13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -3522,7 +3522,7 @@
         <v>33</v>
       </c>
       <c r="M13" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N13" t="s">
         <v>154</v>
@@ -3531,10 +3531,10 @@
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="Q13" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="R13" t="s">
         <v>30</v>
@@ -3549,7 +3549,7 @@
         <v>31</v>
       </c>
       <c r="V13" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="W13" t="s">
         <v>33</v>
@@ -3575,16 +3575,16 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
         <v>21</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -3596,7 +3596,7 @@
         <v>33</v>
       </c>
       <c r="M14" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="N14" t="s">
         <v>156</v>
@@ -3605,13 +3605,13 @@
         <v>50</v>
       </c>
       <c r="P14" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="Q14" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="R14" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -3623,7 +3623,7 @@
         <v>31</v>
       </c>
       <c r="V14" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="W14" t="s">
         <v>33</v>
@@ -3649,16 +3649,16 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
         <v>21</v>
       </c>
       <c r="I15" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -3670,7 +3670,7 @@
         <v>33</v>
       </c>
       <c r="M15" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N15" t="s">
         <v>140</v>
@@ -3679,10 +3679,10 @@
         <v>65</v>
       </c>
       <c r="P15" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="Q15" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="R15" t="s">
         <v>30</v>
@@ -3697,7 +3697,7 @@
         <v>31</v>
       </c>
       <c r="V15" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="W15" t="s">
         <v>33</v>
@@ -3723,16 +3723,16 @@
         <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
         <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -3744,7 +3744,7 @@
         <v>33</v>
       </c>
       <c r="M16" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N16" t="s">
         <v>137</v>
@@ -3753,10 +3753,10 @@
         <v>65</v>
       </c>
       <c r="P16" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="Q16" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="R16" t="s">
         <v>30</v>
@@ -3797,16 +3797,16 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="I17" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -3818,7 +3818,7 @@
         <v>33</v>
       </c>
       <c r="M17" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N17" t="s">
         <v>160</v>
@@ -3827,10 +3827,10 @@
         <v>65</v>
       </c>
       <c r="P17" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="Q17" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="R17" t="s">
         <v>30</v>
@@ -3845,7 +3845,7 @@
         <v>31</v>
       </c>
       <c r="V17" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="W17" t="s">
         <v>33</v>
@@ -3871,16 +3871,16 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="H18" t="s">
         <v>21</v>
       </c>
       <c r="I18" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -3892,7 +3892,7 @@
         <v>33</v>
       </c>
       <c r="M18" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N18" t="s">
         <v>140</v>
@@ -3901,10 +3901,10 @@
         <v>65</v>
       </c>
       <c r="P18" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="Q18" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="R18" t="s">
         <v>30</v>
@@ -3919,7 +3919,7 @@
         <v>31</v>
       </c>
       <c r="V18" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="W18" t="s">
         <v>33</v>
@@ -3945,16 +3945,16 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s">
         <v>34</v>
       </c>
       <c r="I19" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -3966,7 +3966,7 @@
         <v>33</v>
       </c>
       <c r="M19" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N19" t="s">
         <v>143</v>
@@ -3975,10 +3975,10 @@
         <v>100</v>
       </c>
       <c r="P19" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="Q19" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="R19" t="s">
         <v>30</v>
@@ -4013,22 +4013,22 @@
         <v>134</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
         <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="H20" t="s">
         <v>21</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -4040,7 +4040,7 @@
         <v>33</v>
       </c>
       <c r="M20" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N20" t="s">
         <v>135</v>
@@ -4049,10 +4049,10 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="Q20" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="R20" t="s">
         <v>30</v>
@@ -4087,22 +4087,22 @@
         <v>134</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
         <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="G21" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
         <v>21</v>
       </c>
       <c r="I21" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -4114,7 +4114,7 @@
         <v>33</v>
       </c>
       <c r="M21" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N21" t="s">
         <v>135</v>
@@ -4123,10 +4123,10 @@
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="Q21" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="R21" t="s">
         <v>30</v>
@@ -4161,22 +4161,22 @@
         <v>134</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="H22" t="s">
         <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -4188,7 +4188,7 @@
         <v>33</v>
       </c>
       <c r="M22" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="N22" t="s">
         <v>152</v>
@@ -4197,10 +4197,10 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="Q22" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="R22" t="s">
         <v>30</v>
@@ -4215,7 +4215,7 @@
         <v>31</v>
       </c>
       <c r="V22" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="W22" t="s">
         <v>33</v>
@@ -4235,22 +4235,22 @@
         <v>134</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s">
         <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="G23" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s">
         <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -4262,7 +4262,7 @@
         <v>33</v>
       </c>
       <c r="M23" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="N23" t="s">
         <v>140</v>
@@ -4271,10 +4271,10 @@
         <v>65</v>
       </c>
       <c r="P23" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="Q23" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="R23" t="s">
         <v>30</v>
@@ -4289,7 +4289,7 @@
         <v>31</v>
       </c>
       <c r="V23" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="W23" t="s">
         <v>33</v>
@@ -5049,7 +5049,7 @@
         <v>33</v>
       </c>
       <c r="N11" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="O11" t="s">
         <v>194</v>
@@ -5111,7 +5111,7 @@
         <v>33</v>
       </c>
       <c r="N12" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="O12" t="s">
         <v>194</v>
@@ -5173,7 +5173,7 @@
         <v>33</v>
       </c>
       <c r="N13" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="O13" t="s">
         <v>194</v>
@@ -5208,7 +5208,7 @@
         <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="F14" t="s">
         <v>33</v>
@@ -5273,7 +5273,7 @@
         <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
         <v>33</v>
@@ -5332,7 +5332,7 @@
         <v>33</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="F16" t="s">
         <v>193</v>
@@ -5394,7 +5394,7 @@
         <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s">
         <v>193</v>
@@ -5545,7 +5545,7 @@
         <v>33</v>
       </c>
       <c r="N19" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="O19" t="s">
         <v>33</v>
@@ -5669,7 +5669,7 @@
         <v>33</v>
       </c>
       <c r="N21" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="O21" t="s">
         <v>33</v>
@@ -5814,7 +5814,7 @@
         <v>247</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
@@ -5934,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
         <v>255</v>
@@ -6074,7 +6074,7 @@
         <v>258</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
         <v>266</v>

--- a/apps/web/public/examples/example-with-constraint-rules.xlsx
+++ b/apps/web/public/examples/example-with-constraint-rules.xlsx
@@ -844,7 +844,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:26:04</t>
+    <t>08:32:09</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-with-constraint-rules.xlsx
+++ b/apps/web/public/examples/example-with-constraint-rules.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="299">
   <si>
     <t>Term</t>
   </si>
@@ -331,6 +331,21 @@
     <t>Kim teaches three in a row on MWF</t>
   </si>
   <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>SB 123</t>
+  </si>
+  <si>
+    <t>Urban Seminar</t>
+  </si>
+  <si>
+    <t>Hal Fakename</t>
+  </si>
+  <si>
+    <t>A seminar run as a 200- and a 300-level course: same instructor, room and time; allowed by this department's rule</t>
+  </si>
+  <si>
     <t>315</t>
   </si>
   <si>
@@ -343,6 +358,15 @@
     <t>Planning Algorithms</t>
   </si>
   <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>The 300-level listing of the seminar; its load is counted with CRUD 290</t>
+  </si>
+  <si>
     <t>DIGI</t>
   </si>
   <si>
@@ -376,9 +400,6 @@
     <t>Ecology Core</t>
   </si>
   <si>
-    <t>Hal Fakename</t>
-  </si>
-  <si>
     <t>There is no evening section yet</t>
   </si>
   <si>
@@ -520,6 +541,12 @@
     <t>AY25-SP-BHAV226-A</t>
   </si>
   <si>
+    <t>AY25-FA-CRUD290-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-CRUD390-A</t>
+  </si>
+  <si>
     <t>Activity</t>
   </si>
   <si>
@@ -745,6 +772,21 @@
     <t>AMUS 296 is meant to meet on only one of the standard days, so it is not flagged for that.</t>
   </si>
   <si>
+    <t>The seminar runs at two levels</t>
+  </si>
+  <si>
+    <t>collide</t>
+  </si>
+  <si>
+    <t>CRUD 290</t>
+  </si>
+  <si>
+    <t>CRUD 290 and CRUD 390 are one class, so they share an instructor, a room and a time on purpose.</t>
+  </si>
+  <si>
+    <t>CRUD 390</t>
+  </si>
+  <si>
     <t>Kind</t>
   </si>
   <si>
@@ -844,7 +886,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:32:09</t>
+    <t>21:03:16</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -1252,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2301,13 +2343,13 @@
         <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H19" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19" t="s">
         <v>105</v>
-      </c>
-      <c r="I19" t="s">
-        <v>106</v>
       </c>
       <c r="J19" t="s">
         <v>26</v>
@@ -2316,13 +2358,13 @@
         <v>27</v>
       </c>
       <c r="L19">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M19" t="s">
+        <v>106</v>
+      </c>
+      <c r="N19" t="s">
         <v>107</v>
-      </c>
-      <c r="N19" t="s">
-        <v>95</v>
       </c>
       <c r="O19" t="s">
         <v>30</v>
@@ -2331,7 +2373,7 @@
         <v>31</v>
       </c>
       <c r="Q19" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="R19" t="s">
         <v>33</v>
@@ -2342,7 +2384,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
         <v>109</v>
@@ -2360,10 +2402,10 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="I20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J20" t="s">
         <v>26</v>
@@ -2372,13 +2414,13 @@
         <v>27</v>
       </c>
       <c r="L20">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N20" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="O20" t="s">
         <v>30</v>
@@ -2398,10 +2440,10 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
         <v>21</v>
@@ -2410,16 +2452,16 @@
         <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>22</v>
+        <v>114</v>
       </c>
       <c r="G21" t="s">
         <v>23</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="I21" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="J21" t="s">
         <v>26</v>
@@ -2431,10 +2473,10 @@
         <v>100</v>
       </c>
       <c r="M21" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="N21" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="O21" t="s">
         <v>30</v>
@@ -2443,7 +2485,7 @@
         <v>31</v>
       </c>
       <c r="Q21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="R21" t="s">
         <v>33</v>
@@ -2454,10 +2496,10 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
         <v>21</v>
@@ -2472,10 +2514,10 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J22" t="s">
         <v>26</v>
@@ -2487,10 +2529,10 @@
         <v>65</v>
       </c>
       <c r="M22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O22" t="s">
         <v>30</v>
@@ -2499,7 +2541,7 @@
         <v>31</v>
       </c>
       <c r="Q22" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="R22" t="s">
         <v>33</v>
@@ -2510,13 +2552,13 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
         <v>22</v>
@@ -2531,7 +2573,7 @@
         <v>87</v>
       </c>
       <c r="I23" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="J23" t="s">
         <v>26</v>
@@ -2543,10 +2585,10 @@
         <v>100</v>
       </c>
       <c r="M23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N23" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="O23" t="s">
         <v>30</v>
@@ -2555,9 +2597,121 @@
         <v>31</v>
       </c>
       <c r="Q23" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="R23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" t="s">
+        <v>125</v>
+      </c>
+      <c r="J24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" t="s">
+        <v>27</v>
+      </c>
+      <c r="L24">
+        <v>65</v>
+      </c>
+      <c r="M24" t="s">
+        <v>126</v>
+      </c>
+      <c r="N24" t="s">
+        <v>107</v>
+      </c>
+      <c r="O24" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>127</v>
+      </c>
+      <c r="R24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" t="s">
+        <v>87</v>
+      </c>
+      <c r="I25" t="s">
+        <v>125</v>
+      </c>
+      <c r="J25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25">
+        <v>100</v>
+      </c>
+      <c r="M25" t="s">
+        <v>126</v>
+      </c>
+      <c r="N25" t="s">
+        <v>107</v>
+      </c>
+      <c r="O25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P25" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>33</v>
+      </c>
+      <c r="R25" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2569,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -2598,13 +2752,13 @@
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -2628,22 +2782,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -2652,10 +2806,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -2664,21 +2818,21 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
@@ -2711,7 +2865,7 @@
         <v>23</v>
       </c>
       <c r="N2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="O2">
         <v>100</v>
@@ -2746,13 +2900,13 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -2785,7 +2939,7 @@
         <v>35</v>
       </c>
       <c r="N3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="O3">
         <v>65</v>
@@ -2820,13 +2974,13 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
         <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -2859,7 +3013,7 @@
         <v>23</v>
       </c>
       <c r="N4" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -2894,13 +3048,13 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
@@ -2933,7 +3087,7 @@
         <v>35</v>
       </c>
       <c r="N5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="O5">
         <v>65</v>
@@ -2968,13 +3122,13 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>141</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>134</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -2983,16 +3137,16 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G6" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H6" t="s">
         <v>21</v>
       </c>
       <c r="I6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3007,16 +3161,16 @@
         <v>35</v>
       </c>
       <c r="N6" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="Q6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="R6" t="s">
         <v>30</v>
@@ -3042,13 +3196,13 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -3057,7 +3211,7 @@
         <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G7" t="s">
         <v>60</v>
@@ -3081,7 +3235,7 @@
         <v>23</v>
       </c>
       <c r="N7" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3090,7 +3244,7 @@
         <v>67</v>
       </c>
       <c r="Q7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="R7" t="s">
         <v>30</v>
@@ -3105,7 +3259,7 @@
         <v>31</v>
       </c>
       <c r="V7" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="W7" t="s">
         <v>33</v>
@@ -3116,13 +3270,13 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -3155,7 +3309,7 @@
         <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -3190,13 +3344,13 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -3229,7 +3383,7 @@
         <v>35</v>
       </c>
       <c r="N9" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="O9">
         <v>65</v>
@@ -3264,13 +3418,13 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -3303,7 +3457,7 @@
         <v>35</v>
       </c>
       <c r="N10" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="O10">
         <v>65</v>
@@ -3338,13 +3492,13 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -3356,7 +3510,7 @@
         <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H11" t="s">
         <v>21</v>
@@ -3377,16 +3531,16 @@
         <v>35</v>
       </c>
       <c r="N11" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="O11">
         <v>60</v>
       </c>
       <c r="P11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="Q11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="R11" t="s">
         <v>30</v>
@@ -3412,13 +3566,13 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -3451,7 +3605,7 @@
         <v>35</v>
       </c>
       <c r="N12" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="O12">
         <v>65</v>
@@ -3486,13 +3640,13 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -3525,7 +3679,7 @@
         <v>23</v>
       </c>
       <c r="N13" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -3560,13 +3714,13 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -3599,7 +3753,7 @@
         <v>45</v>
       </c>
       <c r="N14" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O14">
         <v>50</v>
@@ -3634,13 +3788,13 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -3673,7 +3827,7 @@
         <v>35</v>
       </c>
       <c r="N15" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="O15">
         <v>65</v>
@@ -3708,13 +3862,13 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -3747,7 +3901,7 @@
         <v>35</v>
       </c>
       <c r="N16" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="O16">
         <v>65</v>
@@ -3782,13 +3936,13 @@
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -3821,7 +3975,7 @@
         <v>35</v>
       </c>
       <c r="N17" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="O17">
         <v>65</v>
@@ -3856,13 +4010,13 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -3871,16 +4025,16 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G18" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="H18" t="s">
         <v>21</v>
       </c>
       <c r="I18" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -3895,16 +4049,16 @@
         <v>35</v>
       </c>
       <c r="N18" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="O18">
         <v>65</v>
       </c>
       <c r="P18" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="Q18" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="R18" t="s">
         <v>30</v>
@@ -3919,7 +4073,7 @@
         <v>31</v>
       </c>
       <c r="V18" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="W18" t="s">
         <v>33</v>
@@ -3930,13 +4084,13 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -3945,16 +4099,16 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G19" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="H19" t="s">
         <v>34</v>
       </c>
       <c r="I19" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -3969,16 +4123,16 @@
         <v>23</v>
       </c>
       <c r="N19" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="Q19" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="R19" t="s">
         <v>30</v>
@@ -4004,13 +4158,13 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D20" t="s">
         <v>38</v>
@@ -4043,7 +4197,7 @@
         <v>23</v>
       </c>
       <c r="N20" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -4078,13 +4232,13 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
         <v>38</v>
@@ -4117,7 +4271,7 @@
         <v>23</v>
       </c>
       <c r="N21" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -4152,13 +4306,13 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
         <v>38</v>
@@ -4191,7 +4345,7 @@
         <v>56</v>
       </c>
       <c r="N22" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -4226,13 +4380,13 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D23" t="s">
         <v>38</v>
@@ -4265,7 +4419,7 @@
         <v>83</v>
       </c>
       <c r="N23" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="O23">
         <v>65</v>
@@ -4295,6 +4449,154 @@
         <v>33</v>
       </c>
       <c r="X23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s">
+        <v>107</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24">
+        <v>4</v>
+      </c>
+      <c r="L24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M24" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" t="s">
+        <v>161</v>
+      </c>
+      <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="P24" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>106</v>
+      </c>
+      <c r="R24" t="s">
+        <v>30</v>
+      </c>
+      <c r="S24" t="s">
+        <v>33</v>
+      </c>
+      <c r="T24" t="s">
+        <v>33</v>
+      </c>
+      <c r="U24" t="s">
+        <v>31</v>
+      </c>
+      <c r="V24" t="s">
+        <v>108</v>
+      </c>
+      <c r="W24" t="s">
+        <v>33</v>
+      </c>
+      <c r="X24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>175</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" t="s">
+        <v>113</v>
+      </c>
+      <c r="H25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" t="s">
+        <v>107</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>4</v>
+      </c>
+      <c r="L25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N25" t="s">
+        <v>161</v>
+      </c>
+      <c r="O25">
+        <v>100</v>
+      </c>
+      <c r="P25" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>106</v>
+      </c>
+      <c r="R25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S25" t="s">
+        <v>33</v>
+      </c>
+      <c r="T25" t="s">
+        <v>33</v>
+      </c>
+      <c r="U25" t="s">
+        <v>31</v>
+      </c>
+      <c r="V25" t="s">
+        <v>115</v>
+      </c>
+      <c r="W25" t="s">
+        <v>33</v>
+      </c>
+      <c r="X25" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4316,7 +4618,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4343,19 +4645,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -4369,7 +4671,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -4390,61 +4692,61 @@
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>16</v>
@@ -4452,13 +4754,13 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -4509,18 +4811,18 @@
         <v>33</v>
       </c>
       <c r="T2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -4576,13 +4878,13 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -4638,13 +4940,13 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -4653,10 +4955,10 @@
         <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G5" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="H5" t="s">
         <v>33</v>
@@ -4695,18 +4997,18 @@
         <v>33</v>
       </c>
       <c r="T5" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B6" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C6" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -4715,10 +5017,10 @@
         <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G6" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="H6" t="s">
         <v>33</v>
@@ -4762,13 +5064,13 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -4777,10 +5079,10 @@
         <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G7" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="H7" t="s">
         <v>33</v>
@@ -4824,13 +5126,13 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -4839,10 +5141,10 @@
         <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G8" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="H8" t="s">
         <v>33</v>
@@ -4881,18 +5183,18 @@
         <v>33</v>
       </c>
       <c r="T8" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C9" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -4901,10 +5203,10 @@
         <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G9" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="H9" t="s">
         <v>33</v>
@@ -4948,13 +5250,13 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -4963,10 +5265,10 @@
         <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G10" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="H10" t="s">
         <v>33</v>
@@ -5010,13 +5312,13 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C11" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -5052,33 +5354,33 @@
         <v>45</v>
       </c>
       <c r="O11" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="P11" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="Q11" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="R11" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="S11" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="T11" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B12" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -5114,19 +5416,19 @@
         <v>45</v>
       </c>
       <c r="O12" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="P12" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="Q12" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="R12" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="S12" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="T12" t="s">
         <v>33</v>
@@ -5134,13 +5436,13 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C13" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D13" t="s">
         <v>33</v>
@@ -5176,19 +5478,19 @@
         <v>45</v>
       </c>
       <c r="O13" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="P13" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="Q13" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="R13" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="S13" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="T13" t="s">
         <v>33</v>
@@ -5196,10 +5498,10 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
@@ -5238,33 +5540,33 @@
         <v>33</v>
       </c>
       <c r="O14" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="P14" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="Q14" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="R14" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="S14" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="T14" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B15" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C15" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D15" t="s">
         <v>33</v>
@@ -5300,30 +5602,30 @@
         <v>33</v>
       </c>
       <c r="O15" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="P15" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="Q15" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="R15" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="S15" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="T15" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B16" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C16" t="s">
         <v>33</v>
@@ -5335,16 +5637,16 @@
         <v>95</v>
       </c>
       <c r="F16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G16" t="s">
         <v>33</v>
       </c>
       <c r="H16" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="I16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="J16" t="s">
         <v>33</v>
@@ -5382,10 +5684,10 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B17" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -5397,16 +5699,16 @@
         <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G17" t="s">
         <v>33</v>
       </c>
       <c r="H17" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="I17" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="J17" t="s">
         <v>33</v>
@@ -5444,13 +5746,13 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B18" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D18" t="s">
         <v>33</v>
@@ -5501,15 +5803,15 @@
         <v>33</v>
       </c>
       <c r="T18" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B19" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
@@ -5533,13 +5835,13 @@
         <v>33</v>
       </c>
       <c r="J19" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="K19" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L19" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="M19" t="s">
         <v>33</v>
@@ -5568,13 +5870,13 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C20" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D20" t="s">
         <v>33</v>
@@ -5625,15 +5927,15 @@
         <v>33</v>
       </c>
       <c r="T20" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -5657,13 +5959,13 @@
         <v>33</v>
       </c>
       <c r="J21" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="K21" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="L21" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="M21" t="s">
         <v>33</v>
@@ -5692,13 +5994,13 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C22" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D22" t="s">
         <v>33</v>
@@ -5749,7 +6051,131 @@
         <v>33</v>
       </c>
       <c r="T22" t="s">
-        <v>241</v>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>251</v>
+      </c>
+      <c r="B23" t="s">
+        <v>252</v>
+      </c>
+      <c r="C23" t="s">
+        <v>253</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" t="s">
+        <v>33</v>
+      </c>
+      <c r="K23" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" t="s">
+        <v>33</v>
+      </c>
+      <c r="M23" t="s">
+        <v>33</v>
+      </c>
+      <c r="N23" t="s">
+        <v>33</v>
+      </c>
+      <c r="O23" t="s">
+        <v>33</v>
+      </c>
+      <c r="P23" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>33</v>
+      </c>
+      <c r="R23" t="s">
+        <v>33</v>
+      </c>
+      <c r="S23" t="s">
+        <v>33</v>
+      </c>
+      <c r="T23" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>251</v>
+      </c>
+      <c r="B24" t="s">
+        <v>252</v>
+      </c>
+      <c r="C24" t="s">
+        <v>255</v>
+      </c>
+      <c r="D24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N24" t="s">
+        <v>33</v>
+      </c>
+      <c r="O24" t="s">
+        <v>33</v>
+      </c>
+      <c r="P24" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>33</v>
+      </c>
+      <c r="R24" t="s">
+        <v>33</v>
+      </c>
+      <c r="S24" t="s">
+        <v>33</v>
+      </c>
+      <c r="T24" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -5771,27 +6197,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -5811,7 +6237,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B3" t="s">
         <v>38</v>
@@ -5831,10 +6257,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="B4" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
@@ -5851,10 +6277,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="B5" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
@@ -5871,10 +6297,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="B6" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
@@ -5897,7 +6323,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -5914,10 +6340,10 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="C8" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -5937,7 +6363,7 @@
         <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -5954,10 +6380,10 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="C10" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -5971,13 +6397,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -5991,13 +6417,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B12" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="C12" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -6011,13 +6437,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B13" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="C13" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="D13" t="s">
         <v>33</v>
@@ -6031,13 +6457,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="D14" t="s">
         <v>33</v>
@@ -6051,13 +6477,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="D15" t="s">
         <v>33</v>
@@ -6071,13 +6497,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="D16" t="s">
         <v>33</v>
@@ -6091,13 +6517,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B17" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C17" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="D17" t="s">
         <v>33</v>
@@ -6111,16 +6537,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="D18" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6146,39 +6572,39 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B2" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B3" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
@@ -6186,7 +6612,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -6194,23 +6620,23 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B7" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="B8" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
@@ -6218,7 +6644,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
@@ -6226,7 +6652,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>

--- a/apps/web/public/examples/example-with-constraint-rules.xlsx
+++ b/apps/web/public/examples/example-with-constraint-rules.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="303">
   <si>
     <t>Term</t>
   </si>
@@ -73,6 +73,15 @@
     <t>CrossListings</t>
   </si>
   <si>
+    <t>CoreTag</t>
+  </si>
+  <si>
+    <t>SpecialTopic</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
     <t>FA</t>
   </si>
   <si>
@@ -121,6 +130,9 @@
     <t/>
   </si>
   <si>
+    <t>UGRAD</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
@@ -775,7 +787,7 @@
     <t>The seminar runs at two levels</t>
   </si>
   <si>
-    <t>collide</t>
+    <t>colocate</t>
   </si>
   <si>
     <t>CRUD 290</t>
@@ -880,13 +892,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-04</t>
+    <t>2026-10-06</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>21:03:16</t>
+    <t>13:27:37</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -1294,7 +1306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1313,9 +1325,11 @@
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="40" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1370,1349 +1384,1574 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L2">
         <v>100</v>
       </c>
       <c r="M2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
+      <c r="J3" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
+      <c r="K3" t="s">
         <v>30</v>
-      </c>
-      <c r="P2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
       </c>
       <c r="L3">
         <v>65</v>
       </c>
       <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>41</v>
+      </c>
+      <c r="R3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="N3" t="s">
+      <c r="J4" t="s">
         <v>29</v>
       </c>
-      <c r="O3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" t="s">
         <v>30</v>
-      </c>
-      <c r="P4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>33</v>
-      </c>
-      <c r="R4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
       </c>
       <c r="L5">
         <v>50</v>
       </c>
       <c r="M5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>54</v>
+      </c>
+      <c r="R5" t="s">
+        <v>36</v>
+      </c>
+      <c r="S5" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" t="s">
+        <v>36</v>
+      </c>
+      <c r="U5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" t="s">
         <v>29</v>
       </c>
-      <c r="O5" t="s">
-        <v>49</v>
-      </c>
-      <c r="P5" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>50</v>
-      </c>
-      <c r="R5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" t="s">
-        <v>26</v>
-      </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L6">
         <v>65</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N6" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" t="s">
+        <v>36</v>
+      </c>
+      <c r="S6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>42</v>
       </c>
-      <c r="O6" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>38</v>
-      </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>63</v>
+      </c>
+      <c r="R7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S7" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" t="s">
+        <v>36</v>
+      </c>
+      <c r="U7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" t="s">
         <v>30</v>
-      </c>
-      <c r="P7" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>59</v>
-      </c>
-      <c r="R7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" t="s">
-        <v>27</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="N8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="O8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>68</v>
+      </c>
+      <c r="R8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" t="s">
+        <v>36</v>
+      </c>
+      <c r="U8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" t="s">
         <v>30</v>
-      </c>
-      <c r="P8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>64</v>
-      </c>
-      <c r="R8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" t="s">
-        <v>27</v>
       </c>
       <c r="L9">
         <v>65</v>
       </c>
       <c r="M9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O9" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>74</v>
+      </c>
+      <c r="R9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>69</v>
       </c>
-      <c r="O9" t="s">
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" t="s">
         <v>30</v>
-      </c>
-      <c r="P9" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>70</v>
-      </c>
-      <c r="R9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" t="s">
-        <v>27</v>
       </c>
       <c r="L10">
         <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N10" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10" t="s">
+        <v>33</v>
+      </c>
+      <c r="P10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" t="s">
+        <v>36</v>
+      </c>
+      <c r="S10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" t="s">
+        <v>36</v>
+      </c>
+      <c r="U10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
         <v>69</v>
       </c>
-      <c r="O10" t="s">
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" t="s">
         <v>30</v>
-      </c>
-      <c r="P10" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>33</v>
-      </c>
-      <c r="R10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" t="s">
-        <v>72</v>
-      </c>
-      <c r="I11" t="s">
-        <v>73</v>
-      </c>
-      <c r="J11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" t="s">
-        <v>27</v>
       </c>
       <c r="L11">
         <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="O11" t="s">
+        <v>33</v>
+      </c>
+      <c r="P11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>79</v>
+      </c>
+      <c r="R11" t="s">
+        <v>36</v>
+      </c>
+      <c r="S11" t="s">
+        <v>36</v>
+      </c>
+      <c r="T11" t="s">
+        <v>36</v>
+      </c>
+      <c r="U11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" t="s">
         <v>30</v>
-      </c>
-      <c r="P11" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>75</v>
-      </c>
-      <c r="R11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" t="s">
-        <v>77</v>
-      </c>
-      <c r="J12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" t="s">
-        <v>27</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="N12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="O12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="S12" t="s">
+        <v>36</v>
+      </c>
+      <c r="T12" t="s">
+        <v>36</v>
+      </c>
+      <c r="U12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I13" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13" t="s">
+        <v>85</v>
+      </c>
+      <c r="N13" t="s">
+        <v>83</v>
+      </c>
+      <c r="O13" t="s">
+        <v>33</v>
+      </c>
+      <c r="P13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>36</v>
+      </c>
+      <c r="R13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S13" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" t="s">
+        <v>36</v>
+      </c>
+      <c r="U13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" t="s">
         <v>81</v>
       </c>
-      <c r="N13" t="s">
-        <v>79</v>
-      </c>
-      <c r="O13" t="s">
-        <v>30</v>
-      </c>
-      <c r="P13" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>33</v>
-      </c>
-      <c r="R13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" t="s">
-        <v>77</v>
-      </c>
       <c r="J14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L14">
         <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="O14" t="s">
+        <v>33</v>
+      </c>
+      <c r="P14" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>89</v>
+      </c>
+      <c r="R14" t="s">
+        <v>36</v>
+      </c>
+      <c r="S14" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" t="s">
+        <v>36</v>
+      </c>
+      <c r="U14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" t="s">
         <v>30</v>
-      </c>
-      <c r="P14" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>85</v>
-      </c>
-      <c r="R14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" t="s">
-        <v>87</v>
-      </c>
-      <c r="I15" t="s">
-        <v>77</v>
-      </c>
-      <c r="J15" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" t="s">
-        <v>27</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N15" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="O15" t="s">
+        <v>33</v>
+      </c>
+      <c r="P15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>93</v>
+      </c>
+      <c r="R15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S15" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" t="s">
+        <v>36</v>
+      </c>
+      <c r="U15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" t="s">
+        <v>96</v>
+      </c>
+      <c r="I16" t="s">
+        <v>97</v>
+      </c>
+      <c r="J16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" t="s">
         <v>30</v>
-      </c>
-      <c r="P15" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>89</v>
-      </c>
-      <c r="R15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I16" t="s">
-        <v>93</v>
-      </c>
-      <c r="J16" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" t="s">
-        <v>27</v>
       </c>
       <c r="L16">
         <v>65</v>
       </c>
       <c r="M16" t="s">
+        <v>98</v>
+      </c>
+      <c r="N16" t="s">
+        <v>99</v>
+      </c>
+      <c r="O16" t="s">
+        <v>33</v>
+      </c>
+      <c r="P16" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>36</v>
+      </c>
+      <c r="R16" t="s">
+        <v>36</v>
+      </c>
+      <c r="S16" t="s">
+        <v>36</v>
+      </c>
+      <c r="T16" t="s">
+        <v>36</v>
+      </c>
+      <c r="U16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
         <v>94</v>
       </c>
-      <c r="N16" t="s">
+      <c r="C17" t="s">
         <v>95</v>
       </c>
-      <c r="O16" t="s">
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" t="s">
+        <v>100</v>
+      </c>
+      <c r="I17" t="s">
+        <v>101</v>
+      </c>
+      <c r="J17" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" t="s">
         <v>30</v>
-      </c>
-      <c r="P16" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" t="s">
-        <v>96</v>
-      </c>
-      <c r="I17" t="s">
-        <v>97</v>
-      </c>
-      <c r="J17" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" t="s">
-        <v>27</v>
       </c>
       <c r="L17">
         <v>65</v>
       </c>
       <c r="M17" t="s">
+        <v>98</v>
+      </c>
+      <c r="N17" t="s">
+        <v>102</v>
+      </c>
+      <c r="O17" t="s">
+        <v>33</v>
+      </c>
+      <c r="P17" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>103</v>
+      </c>
+      <c r="R17" t="s">
+        <v>36</v>
+      </c>
+      <c r="S17" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" t="s">
+        <v>36</v>
+      </c>
+      <c r="U17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
         <v>94</v>
       </c>
-      <c r="N17" t="s">
-        <v>98</v>
-      </c>
-      <c r="O17" t="s">
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" t="s">
+        <v>97</v>
+      </c>
+      <c r="J18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" t="s">
         <v>30</v>
-      </c>
-      <c r="P17" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>99</v>
-      </c>
-      <c r="R17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" t="s">
-        <v>101</v>
-      </c>
-      <c r="I18" t="s">
-        <v>93</v>
-      </c>
-      <c r="J18" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" t="s">
-        <v>27</v>
       </c>
       <c r="L18">
         <v>65</v>
       </c>
       <c r="M18" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="N18" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="O18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>107</v>
+      </c>
+      <c r="R18" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" t="s">
+        <v>36</v>
+      </c>
+      <c r="U18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" t="s">
+        <v>109</v>
+      </c>
+      <c r="J19" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" t="s">
         <v>30</v>
-      </c>
-      <c r="P18" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>103</v>
-      </c>
-      <c r="R18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I19" t="s">
-        <v>105</v>
-      </c>
-      <c r="J19" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" t="s">
-        <v>27</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="N19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O19" t="s">
+        <v>33</v>
+      </c>
+      <c r="P19" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>112</v>
+      </c>
+      <c r="R19" t="s">
+        <v>36</v>
+      </c>
+      <c r="S19" t="s">
+        <v>36</v>
+      </c>
+      <c r="T19" t="s">
+        <v>36</v>
+      </c>
+      <c r="U19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" t="s">
+        <v>114</v>
+      </c>
+      <c r="I20" t="s">
+        <v>115</v>
+      </c>
+      <c r="J20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" t="s">
         <v>30</v>
-      </c>
-      <c r="P19" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>108</v>
-      </c>
-      <c r="R19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" t="s">
-        <v>109</v>
-      </c>
-      <c r="D20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" t="s">
-        <v>110</v>
-      </c>
-      <c r="I20" t="s">
-        <v>111</v>
-      </c>
-      <c r="J20" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" t="s">
-        <v>27</v>
       </c>
       <c r="L20">
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N20" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="O20" t="s">
+        <v>33</v>
+      </c>
+      <c r="P20" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>36</v>
+      </c>
+      <c r="R20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S20" t="s">
+        <v>36</v>
+      </c>
+      <c r="T20" t="s">
+        <v>36</v>
+      </c>
+      <c r="U20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I21" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" t="s">
         <v>30</v>
-      </c>
-      <c r="P20" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>33</v>
-      </c>
-      <c r="R20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" t="s">
-        <v>114</v>
-      </c>
-      <c r="G21" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" t="s">
-        <v>61</v>
-      </c>
-      <c r="I21" t="s">
-        <v>105</v>
-      </c>
-      <c r="J21" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" t="s">
-        <v>27</v>
       </c>
       <c r="L21">
         <v>100</v>
       </c>
       <c r="M21" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="N21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O21" t="s">
+        <v>33</v>
+      </c>
+      <c r="P21" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>119</v>
+      </c>
+      <c r="R21" t="s">
+        <v>36</v>
+      </c>
+      <c r="S21" t="s">
+        <v>36</v>
+      </c>
+      <c r="T21" t="s">
+        <v>36</v>
+      </c>
+      <c r="U21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" t="s">
+        <v>40</v>
+      </c>
+      <c r="I22" t="s">
+        <v>122</v>
+      </c>
+      <c r="J22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" t="s">
         <v>30</v>
-      </c>
-      <c r="P21" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>115</v>
-      </c>
-      <c r="R21" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" t="s">
-        <v>36</v>
-      </c>
-      <c r="I22" t="s">
-        <v>118</v>
-      </c>
-      <c r="J22" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" t="s">
-        <v>27</v>
       </c>
       <c r="L22">
         <v>65</v>
       </c>
       <c r="M22" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N22" t="s">
+        <v>124</v>
+      </c>
+      <c r="O22" t="s">
+        <v>33</v>
+      </c>
+      <c r="P22" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>36</v>
+      </c>
+      <c r="R22" t="s">
+        <v>36</v>
+      </c>
+      <c r="S22" t="s">
+        <v>36</v>
+      </c>
+      <c r="T22" t="s">
+        <v>36</v>
+      </c>
+      <c r="U22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
         <v>120</v>
       </c>
-      <c r="O22" t="s">
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" t="s">
+        <v>71</v>
+      </c>
+      <c r="J23" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" t="s">
         <v>30</v>
-      </c>
-      <c r="P22" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>33</v>
-      </c>
-      <c r="R22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C23" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" t="s">
-        <v>87</v>
-      </c>
-      <c r="I23" t="s">
-        <v>67</v>
-      </c>
-      <c r="J23" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" t="s">
-        <v>27</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="N23" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="O23" t="s">
+        <v>33</v>
+      </c>
+      <c r="P23" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>126</v>
+      </c>
+      <c r="R23" t="s">
+        <v>36</v>
+      </c>
+      <c r="S23" t="s">
+        <v>36</v>
+      </c>
+      <c r="T23" t="s">
+        <v>36</v>
+      </c>
+      <c r="U23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" t="s">
         <v>30</v>
-      </c>
-      <c r="P23" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>122</v>
-      </c>
-      <c r="R23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" t="s">
-        <v>123</v>
-      </c>
-      <c r="C24" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" t="s">
-        <v>35</v>
-      </c>
-      <c r="H24" t="s">
-        <v>52</v>
-      </c>
-      <c r="I24" t="s">
-        <v>125</v>
-      </c>
-      <c r="J24" t="s">
-        <v>26</v>
-      </c>
-      <c r="K24" t="s">
-        <v>27</v>
       </c>
       <c r="L24">
         <v>65</v>
       </c>
       <c r="M24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="N24" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O24" t="s">
+        <v>33</v>
+      </c>
+      <c r="P24" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>131</v>
+      </c>
+      <c r="R24" t="s">
+        <v>36</v>
+      </c>
+      <c r="S24" t="s">
+        <v>36</v>
+      </c>
+      <c r="T24" t="s">
+        <v>36</v>
+      </c>
+      <c r="U24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" t="s">
+        <v>91</v>
+      </c>
+      <c r="I25" t="s">
+        <v>129</v>
+      </c>
+      <c r="J25" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" t="s">
         <v>30</v>
-      </c>
-      <c r="P24" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>127</v>
-      </c>
-      <c r="R24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" t="s">
-        <v>87</v>
-      </c>
-      <c r="I25" t="s">
-        <v>125</v>
-      </c>
-      <c r="J25" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" t="s">
-        <v>27</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="N25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P25" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R25" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="S25" t="s">
+        <v>36</v>
+      </c>
+      <c r="T25" t="s">
+        <v>36</v>
+      </c>
+      <c r="U25" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2723,7 +2962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -2748,17 +2987,18 @@
     <col min="22" max="22" width="40" customWidth="1"/>
     <col min="23" max="23" width="12" customWidth="1"/>
     <col min="24" max="24" width="17" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -2782,22 +3022,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -2806,10 +3046,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -2818,39 +3058,45 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -2859,72 +3105,78 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O2">
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
         <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" t="s">
-        <v>29</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -2933,72 +3185,78 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="O3">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="W3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
         <v>145</v>
       </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>141</v>
-      </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -3007,72 +3265,78 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="R4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -3081,72 +3345,78 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O5">
         <v>65</v>
       </c>
       <c r="P5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="R5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3155,72 +3425,78 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N6" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="Q6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="R6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3229,72 +3505,78 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Q7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="R7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3303,72 +3585,78 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="W8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -3377,72 +3665,78 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O9">
         <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="Q9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="R9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="W9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3451,72 +3745,78 @@
         <v>4</v>
       </c>
       <c r="L10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O10">
         <v>65</v>
       </c>
       <c r="P10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="Q10" t="s">
+        <v>98</v>
+      </c>
+      <c r="R10" t="s">
+        <v>33</v>
+      </c>
+      <c r="S10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" t="s">
+        <v>36</v>
+      </c>
+      <c r="U10" t="s">
+        <v>34</v>
+      </c>
+      <c r="V10" t="s">
+        <v>36</v>
+      </c>
+      <c r="W10" t="s">
+        <v>36</v>
+      </c>
+      <c r="X10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
         <v>94</v>
       </c>
-      <c r="R10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" t="s">
-        <v>33</v>
-      </c>
-      <c r="T10" t="s">
-        <v>33</v>
-      </c>
-      <c r="U10" t="s">
-        <v>31</v>
-      </c>
-      <c r="V10" t="s">
-        <v>33</v>
-      </c>
-      <c r="W10" t="s">
-        <v>33</v>
-      </c>
-      <c r="X10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" t="s">
-        <v>90</v>
-      </c>
       <c r="G11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3525,72 +3825,78 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O11">
         <v>60</v>
       </c>
       <c r="P11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Q11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="R11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G12" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -3599,72 +3905,78 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O12">
         <v>65</v>
       </c>
       <c r="P12" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="Q12" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="R12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="W12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -3673,72 +3985,78 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="R13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="W13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -3747,72 +4065,78 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N14" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O14">
         <v>50</v>
       </c>
       <c r="P14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q14" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="R14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="S14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="W14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -3821,72 +4145,78 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N15" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O15">
         <v>65</v>
       </c>
       <c r="P15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Q15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V15" t="s">
+        <v>74</v>
+      </c>
+      <c r="W15" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" t="s">
         <v>70</v>
       </c>
-      <c r="W15" t="s">
-        <v>33</v>
-      </c>
-      <c r="X15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>141</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" t="s">
-        <v>66</v>
-      </c>
       <c r="H16" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -3895,72 +4225,78 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="O16">
         <v>65</v>
       </c>
       <c r="P16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Q16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R16" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -3969,72 +4305,78 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M17" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N17" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="O17">
         <v>65</v>
       </c>
       <c r="P17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q17" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R17" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="W17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G18" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I18" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -4043,72 +4385,78 @@
         <v>4</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M18" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N18" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O18">
         <v>65</v>
       </c>
       <c r="P18" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Q18" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="R18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U18" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V18" t="s">
+        <v>131</v>
+      </c>
+      <c r="W18" t="s">
+        <v>36</v>
+      </c>
+      <c r="X18" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" t="s">
         <v>127</v>
       </c>
-      <c r="W18" t="s">
-        <v>33</v>
-      </c>
-      <c r="X18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>169</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>141</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" t="s">
-        <v>123</v>
-      </c>
       <c r="G19" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -4117,72 +4465,78 @@
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Q19" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="R19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -4191,72 +4545,78 @@
         <v>4</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N20" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q20" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U20" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I21" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -4265,72 +4625,78 @@
         <v>4</v>
       </c>
       <c r="L21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N21" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q21" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="R21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U21" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G22" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I22" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -4339,72 +4705,78 @@
         <v>4</v>
       </c>
       <c r="L22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M22" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N22" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q22" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="R22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U22" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V22" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="W22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G23" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -4413,72 +4785,78 @@
         <v>4</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M23" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N23" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O23">
         <v>65</v>
       </c>
       <c r="P23" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q23" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R23" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U23" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V23" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="W23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I24" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -4487,72 +4865,78 @@
         <v>4</v>
       </c>
       <c r="L24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N24" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Q24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="R24" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U24" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V24" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="W24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H25" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4561,43 +4945,49 @@
         <v>4</v>
       </c>
       <c r="L25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M25" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Q25" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="R25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U25" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="W25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X25" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -4618,7 +5008,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4645,19 +5035,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -4692,61 +5082,61 @@
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>16</v>
@@ -4754,1428 +5144,1428 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G6" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
         <v>206</v>
       </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" t="s">
-        <v>202</v>
-      </c>
       <c r="G7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B8" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G8" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T8" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B9" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G9" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" t="s">
         <v>206</v>
       </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>202</v>
-      </c>
       <c r="G10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B11" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C11" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N11" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O11" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="P11" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="Q11" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="R11" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="S11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="T11" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B12" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" t="s">
+        <v>36</v>
+      </c>
+      <c r="M12" t="s">
+        <v>36</v>
+      </c>
+      <c r="N12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O12" t="s">
+        <v>207</v>
+      </c>
+      <c r="P12" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q12" t="s">
         <v>217</v>
       </c>
-      <c r="D12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M12" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" t="s">
-        <v>45</v>
-      </c>
-      <c r="O12" t="s">
-        <v>203</v>
-      </c>
-      <c r="P12" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>213</v>
-      </c>
       <c r="R12" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="S12" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="T12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" t="s">
+        <v>49</v>
+      </c>
+      <c r="O13" t="s">
+        <v>207</v>
+      </c>
+      <c r="P13" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>217</v>
+      </c>
+      <c r="R13" t="s">
         <v>218</v>
       </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K13" t="s">
-        <v>33</v>
-      </c>
-      <c r="L13" t="s">
-        <v>33</v>
-      </c>
-      <c r="M13" t="s">
-        <v>33</v>
-      </c>
-      <c r="N13" t="s">
-        <v>45</v>
-      </c>
-      <c r="O13" t="s">
-        <v>203</v>
-      </c>
-      <c r="P13" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>213</v>
-      </c>
-      <c r="R13" t="s">
-        <v>214</v>
-      </c>
       <c r="S13" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="T13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" t="s">
+        <v>36</v>
+      </c>
+      <c r="M14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" t="s">
+        <v>36</v>
+      </c>
+      <c r="O14" t="s">
+        <v>207</v>
+      </c>
+      <c r="P14" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>225</v>
+      </c>
+      <c r="R14" t="s">
+        <v>218</v>
+      </c>
+      <c r="S14" t="s">
         <v>219</v>
       </c>
-      <c r="B14" t="s">
-        <v>211</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" t="s">
-        <v>98</v>
-      </c>
-      <c r="F14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K14" t="s">
-        <v>33</v>
-      </c>
-      <c r="L14" t="s">
-        <v>33</v>
-      </c>
-      <c r="M14" t="s">
-        <v>33</v>
-      </c>
-      <c r="N14" t="s">
-        <v>33</v>
-      </c>
-      <c r="O14" t="s">
-        <v>203</v>
-      </c>
-      <c r="P14" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>221</v>
-      </c>
-      <c r="R14" t="s">
-        <v>214</v>
-      </c>
-      <c r="S14" t="s">
-        <v>215</v>
-      </c>
       <c r="T14" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B15" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O15" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="P15" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q15" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="R15" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="S15" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="T15" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B16" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F16" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H16" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I16" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B17" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="I17" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B18" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C18" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B19" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J19" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K19" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L19" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="M19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N19" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B20" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T20" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J21" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K21" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="L21" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="M21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N21" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="O21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C22" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T22" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B23" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C23" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T23" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C24" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -6197,122 +6587,122 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6320,19 +6710,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6340,19 +6730,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6360,19 +6750,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6380,33 +6770,33 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -6417,16 +6807,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C12" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -6437,16 +6827,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C13" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -6457,16 +6847,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -6477,16 +6867,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -6497,16 +6887,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -6517,16 +6907,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B17" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C17" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E17">
         <v>13</v>
@@ -6537,16 +6927,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D18" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6572,90 +6962,90 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B8" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web/public/examples/example-with-constraint-rules.xlsx
+++ b/apps/web/public/examples/example-with-constraint-rules.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="309">
   <si>
     <t>Term</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Level</t>
   </si>
   <si>
+    <t>Colocations</t>
+  </si>
+  <si>
     <t>FA</t>
   </si>
   <si>
@@ -358,6 +361,9 @@
     <t>A seminar run as a 200- and a 300-level course: same instructor, room and time; allowed by this department's rule</t>
   </si>
   <si>
+    <t>CRUD 390 A</t>
+  </si>
+  <si>
     <t>315</t>
   </si>
   <si>
@@ -379,6 +385,9 @@
     <t>The 300-level listing of the seminar; its load is counted with CRUD 290</t>
   </si>
   <si>
+    <t>CRUD 290 A</t>
+  </si>
+  <si>
     <t>DIGI</t>
   </si>
   <si>
@@ -613,6 +622,15 @@
     <t>Meets</t>
   </si>
   <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
     <t>AMUS major, year 2</t>
   </si>
   <si>
@@ -622,6 +640,9 @@
     <t>AMUS 228</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>A cohort that must be able to take all three courses together. AMUS 228 has two sections so this is met.</t>
   </si>
   <si>
@@ -892,13 +913,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-06</t>
+    <t>2026-10-07</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>13:27:37</t>
+    <t>08:51:36</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -914,9 +935,6 @@
   </si>
   <si>
     <t>Time Stamp In File Name</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
   <si>
     <t>Default Department</t>
@@ -1306,7 +1324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1327,9 +1345,10 @@
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="7" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1393,1564 +1412,1639 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2">
         <v>100</v>
       </c>
       <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
         <v>31</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" t="s">
-        <v>30</v>
       </c>
       <c r="L3">
         <v>65</v>
       </c>
       <c r="M3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5">
         <v>50</v>
       </c>
       <c r="M5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6">
         <v>65</v>
       </c>
       <c r="M6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L9">
         <v>65</v>
       </c>
       <c r="M9" t="s">
+        <v>73</v>
+      </c>
+      <c r="N9" t="s">
+        <v>74</v>
+      </c>
+      <c r="O9" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>75</v>
+      </c>
+      <c r="R9" t="s">
+        <v>37</v>
+      </c>
+      <c r="S9" t="s">
+        <v>37</v>
+      </c>
+      <c r="T9" t="s">
+        <v>37</v>
+      </c>
+      <c r="U9" t="s">
+        <v>38</v>
+      </c>
+      <c r="V9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" t="s">
         <v>72</v>
       </c>
-      <c r="N9" t="s">
-        <v>73</v>
-      </c>
-      <c r="O9" t="s">
-        <v>33</v>
-      </c>
-      <c r="P9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>74</v>
-      </c>
-      <c r="R9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" t="s">
-        <v>71</v>
-      </c>
       <c r="J10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L10">
         <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L11">
         <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12" t="s">
+        <v>83</v>
+      </c>
+      <c r="N12" t="s">
+        <v>84</v>
+      </c>
+      <c r="O12" t="s">
+        <v>34</v>
+      </c>
+      <c r="P12" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>37</v>
+      </c>
+      <c r="R12" t="s">
+        <v>37</v>
+      </c>
+      <c r="S12" t="s">
+        <v>37</v>
+      </c>
+      <c r="T12" t="s">
+        <v>37</v>
+      </c>
+      <c r="U12" t="s">
+        <v>38</v>
+      </c>
+      <c r="V12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" t="s">
         <v>82</v>
       </c>
-      <c r="N12" t="s">
-        <v>83</v>
-      </c>
-      <c r="O12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P12" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>36</v>
-      </c>
-      <c r="R12" t="s">
-        <v>36</v>
-      </c>
-      <c r="S12" t="s">
-        <v>36</v>
-      </c>
-      <c r="T12" t="s">
-        <v>36</v>
-      </c>
-      <c r="U12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" t="s">
-        <v>81</v>
-      </c>
       <c r="J13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L14">
         <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L16">
         <v>65</v>
       </c>
       <c r="M16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L17">
         <v>65</v>
       </c>
       <c r="M17" t="s">
+        <v>99</v>
+      </c>
+      <c r="N17" t="s">
+        <v>103</v>
+      </c>
+      <c r="O17" t="s">
+        <v>34</v>
+      </c>
+      <c r="P17" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>104</v>
+      </c>
+      <c r="R17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S17" t="s">
+        <v>37</v>
+      </c>
+      <c r="T17" t="s">
+        <v>37</v>
+      </c>
+      <c r="U17" t="s">
+        <v>38</v>
+      </c>
+      <c r="V17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" t="s">
         <v>98</v>
       </c>
-      <c r="N17" t="s">
-        <v>102</v>
-      </c>
-      <c r="O17" t="s">
-        <v>33</v>
-      </c>
-      <c r="P17" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>103</v>
-      </c>
-      <c r="R17" t="s">
-        <v>36</v>
-      </c>
-      <c r="S17" t="s">
-        <v>36</v>
-      </c>
-      <c r="T17" t="s">
-        <v>36</v>
-      </c>
-      <c r="U17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" t="s">
-        <v>39</v>
-      </c>
-      <c r="H18" t="s">
-        <v>105</v>
-      </c>
-      <c r="I18" t="s">
-        <v>97</v>
-      </c>
       <c r="J18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L18">
         <v>65</v>
       </c>
       <c r="M18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L20">
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L21">
         <v>100</v>
       </c>
       <c r="M21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="R21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I22" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L22">
         <v>65</v>
       </c>
       <c r="M22" t="s">
+        <v>126</v>
+      </c>
+      <c r="N22" t="s">
+        <v>127</v>
+      </c>
+      <c r="O22" t="s">
+        <v>34</v>
+      </c>
+      <c r="P22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>37</v>
+      </c>
+      <c r="R22" t="s">
+        <v>37</v>
+      </c>
+      <c r="S22" t="s">
+        <v>37</v>
+      </c>
+      <c r="T22" t="s">
+        <v>37</v>
+      </c>
+      <c r="U22" t="s">
+        <v>38</v>
+      </c>
+      <c r="V22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
         <v>123</v>
       </c>
-      <c r="N22" t="s">
-        <v>124</v>
-      </c>
-      <c r="O22" t="s">
-        <v>33</v>
-      </c>
-      <c r="P22" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>36</v>
-      </c>
-      <c r="R22" t="s">
-        <v>36</v>
-      </c>
-      <c r="S22" t="s">
-        <v>36</v>
-      </c>
-      <c r="T22" t="s">
-        <v>36</v>
-      </c>
-      <c r="U22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>120</v>
-      </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="R23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L24">
         <v>65</v>
       </c>
       <c r="M24" t="s">
+        <v>133</v>
+      </c>
+      <c r="N24" t="s">
+        <v>112</v>
+      </c>
+      <c r="O24" t="s">
+        <v>34</v>
+      </c>
+      <c r="P24" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>134</v>
+      </c>
+      <c r="R24" t="s">
+        <v>37</v>
+      </c>
+      <c r="S24" t="s">
+        <v>37</v>
+      </c>
+      <c r="T24" t="s">
+        <v>37</v>
+      </c>
+      <c r="U24" t="s">
+        <v>38</v>
+      </c>
+      <c r="V24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
         <v>130</v>
       </c>
-      <c r="N24" t="s">
-        <v>111</v>
-      </c>
-      <c r="O24" t="s">
-        <v>33</v>
-      </c>
-      <c r="P24" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q24" t="s">
+      <c r="C25" t="s">
         <v>131</v>
       </c>
-      <c r="R24" t="s">
-        <v>36</v>
-      </c>
-      <c r="S24" t="s">
-        <v>36</v>
-      </c>
-      <c r="T24" t="s">
-        <v>36</v>
-      </c>
-      <c r="U24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" t="s">
-        <v>128</v>
-      </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U25" t="s">
+        <v>38</v>
+      </c>
+      <c r="V25" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2992,13 +3086,13 @@
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -3022,22 +3116,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -3046,10 +3140,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -3058,10 +3152,10 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>18</v>
@@ -3072,31 +3166,31 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -3105,78 +3199,78 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O2">
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" t="s">
         <v>36</v>
       </c>
-      <c r="T2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" t="s">
-        <v>34</v>
-      </c>
-      <c r="V2" t="s">
-        <v>35</v>
-      </c>
       <c r="W2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -3185,78 +3279,78 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O3">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -3265,78 +3359,78 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -3345,78 +3439,78 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="O5">
         <v>65</v>
       </c>
       <c r="P5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3425,78 +3519,78 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3505,78 +3599,78 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="R7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="W7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3585,78 +3679,78 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -3665,78 +3759,78 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="O9">
         <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="W9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3745,78 +3839,78 @@
         <v>4</v>
       </c>
       <c r="L10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="O10">
         <v>65</v>
       </c>
       <c r="P10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3825,78 +3919,78 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N11" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O11">
         <v>60</v>
       </c>
       <c r="P11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -3905,78 +3999,78 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="O12">
         <v>65</v>
       </c>
       <c r="P12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -3985,78 +4079,78 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -4065,78 +4159,78 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N14" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="O14">
         <v>50</v>
       </c>
       <c r="P14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4145,78 +4239,78 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N15" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="O15">
         <v>65</v>
       </c>
       <c r="P15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -4225,78 +4319,78 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N16" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O16">
         <v>65</v>
       </c>
       <c r="P16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -4305,78 +4399,78 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="O17">
         <v>65</v>
       </c>
       <c r="P17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G18" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -4385,78 +4479,78 @@
         <v>4</v>
       </c>
       <c r="L18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N18" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="O18">
         <v>65</v>
       </c>
       <c r="P18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q18" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="R18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V18" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="W18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -4465,78 +4559,78 @@
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q19" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="R19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -4545,78 +4639,78 @@
         <v>4</v>
       </c>
       <c r="L20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N20" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" t="s">
         <v>84</v>
-      </c>
-      <c r="H21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I21" t="s">
-        <v>83</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -4625,78 +4719,78 @@
         <v>4</v>
       </c>
       <c r="L21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N21" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -4705,78 +4799,78 @@
         <v>4</v>
       </c>
       <c r="L22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N22" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -4785,78 +4879,78 @@
         <v>4</v>
       </c>
       <c r="L23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N23" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="O23">
         <v>65</v>
       </c>
       <c r="P23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -4865,78 +4959,78 @@
         <v>4</v>
       </c>
       <c r="L24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N24" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="W24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4945,49 +5039,49 @@
         <v>4</v>
       </c>
       <c r="L25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N25" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -5008,7 +5102,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5035,19 +5129,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -5061,7 +5155,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -5077,1495 +5171,1713 @@
     <col min="16" max="17" width="7" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="10" customWidth="1"/>
-    <col min="20" max="20" width="40" customWidth="1"/>
+    <col min="21" max="21" width="10" customWidth="1"/>
+    <col min="22" max="22" width="8" customWidth="1"/>
+    <col min="23" max="23" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" t="s">
+        <v>207</v>
+      </c>
+      <c r="W2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="U3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V3" t="s">
+        <v>207</v>
+      </c>
+      <c r="W3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="U4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" t="s">
+        <v>207</v>
+      </c>
+      <c r="W4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>37</v>
+      </c>
+      <c r="R5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S5" t="s">
+        <v>37</v>
+      </c>
+      <c r="T5" t="s">
+        <v>37</v>
+      </c>
+      <c r="U5" t="s">
+        <v>37</v>
+      </c>
+      <c r="V5" t="s">
+        <v>207</v>
+      </c>
+      <c r="W5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" t="s">
         <v>205</v>
       </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" t="s">
-        <v>206</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="C6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>213</v>
+      </c>
+      <c r="G6" t="s">
+        <v>214</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S6" t="s">
+        <v>37</v>
+      </c>
+      <c r="T6" t="s">
+        <v>37</v>
+      </c>
+      <c r="U6" t="s">
+        <v>37</v>
+      </c>
+      <c r="V6" t="s">
         <v>207</v>
       </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" t="s">
-        <v>36</v>
-      </c>
-      <c r="P5" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R5" t="s">
-        <v>36</v>
-      </c>
-      <c r="S5" t="s">
-        <v>36</v>
-      </c>
-      <c r="T5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>206</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="W6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" t="s">
+        <v>214</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R7" t="s">
+        <v>37</v>
+      </c>
+      <c r="S7" t="s">
+        <v>37</v>
+      </c>
+      <c r="T7" t="s">
+        <v>37</v>
+      </c>
+      <c r="U7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V7" t="s">
         <v>207</v>
       </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N6" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" t="s">
-        <v>36</v>
-      </c>
-      <c r="P6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S6" t="s">
-        <v>36</v>
-      </c>
-      <c r="T6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" t="s">
-        <v>206</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="W7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" t="s">
+        <v>219</v>
+      </c>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" t="s">
+        <v>37</v>
+      </c>
+      <c r="O8" t="s">
+        <v>37</v>
+      </c>
+      <c r="P8" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>37</v>
+      </c>
+      <c r="R8" t="s">
+        <v>37</v>
+      </c>
+      <c r="S8" t="s">
+        <v>37</v>
+      </c>
+      <c r="T8" t="s">
+        <v>37</v>
+      </c>
+      <c r="U8" t="s">
+        <v>37</v>
+      </c>
+      <c r="V8" t="s">
         <v>207</v>
       </c>
-      <c r="H7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" t="s">
-        <v>36</v>
-      </c>
-      <c r="N7" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7" t="s">
-        <v>36</v>
-      </c>
-      <c r="P7" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>36</v>
-      </c>
-      <c r="R7" t="s">
-        <v>36</v>
-      </c>
-      <c r="S7" t="s">
-        <v>36</v>
-      </c>
-      <c r="T7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>211</v>
-      </c>
-      <c r="B8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="W8" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" t="s">
         <v>205</v>
       </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" t="s">
-        <v>206</v>
-      </c>
-      <c r="G8" t="s">
-        <v>212</v>
-      </c>
-      <c r="H8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" t="s">
-        <v>36</v>
-      </c>
-      <c r="N8" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" t="s">
-        <v>36</v>
-      </c>
-      <c r="P8" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>36</v>
-      </c>
-      <c r="R8" t="s">
-        <v>36</v>
-      </c>
-      <c r="S8" t="s">
-        <v>36</v>
-      </c>
-      <c r="T8" t="s">
+      <c r="C9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B9" t="s">
-        <v>199</v>
-      </c>
-      <c r="C9" t="s">
-        <v>209</v>
-      </c>
-      <c r="D9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>206</v>
-      </c>
       <c r="G9" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="U9" t="s">
+        <v>37</v>
+      </c>
+      <c r="V9" t="s">
+        <v>207</v>
+      </c>
+      <c r="W9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="G10" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="U10" t="s">
+        <v>37</v>
+      </c>
+      <c r="V10" t="s">
+        <v>207</v>
+      </c>
+      <c r="W10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" t="s">
+        <v>37</v>
+      </c>
+      <c r="N11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O11" t="s">
         <v>214</v>
       </c>
-      <c r="B11" t="s">
-        <v>215</v>
-      </c>
-      <c r="C11" t="s">
-        <v>216</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" t="s">
-        <v>36</v>
-      </c>
-      <c r="K11" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11" t="s">
-        <v>36</v>
-      </c>
-      <c r="M11" t="s">
-        <v>36</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="P11" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>224</v>
+      </c>
+      <c r="R11" t="s">
+        <v>225</v>
+      </c>
+      <c r="S11" t="s">
+        <v>226</v>
+      </c>
+      <c r="T11" t="s">
+        <v>37</v>
+      </c>
+      <c r="U11" t="s">
+        <v>37</v>
+      </c>
+      <c r="V11" t="s">
+        <v>207</v>
+      </c>
+      <c r="W11" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" t="s">
+        <v>50</v>
+      </c>
+      <c r="O12" t="s">
+        <v>214</v>
+      </c>
+      <c r="P12" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>224</v>
+      </c>
+      <c r="R12" t="s">
+        <v>225</v>
+      </c>
+      <c r="S12" t="s">
+        <v>226</v>
+      </c>
+      <c r="T12" t="s">
+        <v>37</v>
+      </c>
+      <c r="U12" t="s">
+        <v>37</v>
+      </c>
+      <c r="V12" t="s">
+        <v>207</v>
+      </c>
+      <c r="W12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" t="s">
+        <v>50</v>
+      </c>
+      <c r="O13" t="s">
+        <v>214</v>
+      </c>
+      <c r="P13" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>224</v>
+      </c>
+      <c r="R13" t="s">
+        <v>225</v>
+      </c>
+      <c r="S13" t="s">
+        <v>226</v>
+      </c>
+      <c r="T13" t="s">
+        <v>37</v>
+      </c>
+      <c r="U13" t="s">
+        <v>37</v>
+      </c>
+      <c r="V13" t="s">
+        <v>207</v>
+      </c>
+      <c r="W13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" t="s">
+        <v>214</v>
+      </c>
+      <c r="P14" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>232</v>
+      </c>
+      <c r="R14" t="s">
+        <v>225</v>
+      </c>
+      <c r="S14" t="s">
+        <v>226</v>
+      </c>
+      <c r="T14" t="s">
+        <v>37</v>
+      </c>
+      <c r="U14" t="s">
+        <v>37</v>
+      </c>
+      <c r="V14" t="s">
+        <v>207</v>
+      </c>
+      <c r="W14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C15" t="s">
+        <v>235</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" t="s">
         <v>49</v>
       </c>
-      <c r="O11" t="s">
+      <c r="G15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O15" t="s">
+        <v>214</v>
+      </c>
+      <c r="P15" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>237</v>
+      </c>
+      <c r="R15" t="s">
+        <v>238</v>
+      </c>
+      <c r="S15" t="s">
+        <v>239</v>
+      </c>
+      <c r="T15" t="s">
+        <v>37</v>
+      </c>
+      <c r="U15" t="s">
+        <v>37</v>
+      </c>
+      <c r="V15" t="s">
         <v>207</v>
       </c>
-      <c r="P11" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>217</v>
-      </c>
-      <c r="R11" t="s">
-        <v>218</v>
-      </c>
-      <c r="S11" t="s">
-        <v>219</v>
-      </c>
-      <c r="T11" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>214</v>
-      </c>
-      <c r="B12" t="s">
-        <v>215</v>
-      </c>
-      <c r="C12" t="s">
-        <v>221</v>
-      </c>
-      <c r="D12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12" t="s">
-        <v>36</v>
-      </c>
-      <c r="K12" t="s">
-        <v>36</v>
-      </c>
-      <c r="L12" t="s">
-        <v>36</v>
-      </c>
-      <c r="M12" t="s">
-        <v>36</v>
-      </c>
-      <c r="N12" t="s">
-        <v>49</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="W15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" t="s">
+        <v>213</v>
+      </c>
+      <c r="G16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" t="s">
+        <v>243</v>
+      </c>
+      <c r="I16" t="s">
+        <v>244</v>
+      </c>
+      <c r="J16" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" t="s">
+        <v>37</v>
+      </c>
+      <c r="P16" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" t="s">
+        <v>37</v>
+      </c>
+      <c r="S16" t="s">
+        <v>37</v>
+      </c>
+      <c r="T16" t="s">
+        <v>37</v>
+      </c>
+      <c r="U16" t="s">
+        <v>37</v>
+      </c>
+      <c r="V16" t="s">
         <v>207</v>
       </c>
-      <c r="P12" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>217</v>
-      </c>
-      <c r="R12" t="s">
-        <v>218</v>
-      </c>
-      <c r="S12" t="s">
-        <v>219</v>
-      </c>
-      <c r="T12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>214</v>
-      </c>
-      <c r="B13" t="s">
-        <v>215</v>
-      </c>
-      <c r="C13" t="s">
-        <v>222</v>
-      </c>
-      <c r="D13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" t="s">
-        <v>36</v>
-      </c>
-      <c r="K13" t="s">
-        <v>36</v>
-      </c>
-      <c r="L13" t="s">
-        <v>36</v>
-      </c>
-      <c r="M13" t="s">
-        <v>36</v>
-      </c>
-      <c r="N13" t="s">
-        <v>49</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="W16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>245</v>
+      </c>
+      <c r="B17" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" t="s">
+        <v>213</v>
+      </c>
+      <c r="G17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" t="s">
+        <v>246</v>
+      </c>
+      <c r="I17" t="s">
+        <v>244</v>
+      </c>
+      <c r="J17" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17" t="s">
+        <v>37</v>
+      </c>
+      <c r="P17" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>37</v>
+      </c>
+      <c r="R17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S17" t="s">
+        <v>37</v>
+      </c>
+      <c r="T17" t="s">
+        <v>37</v>
+      </c>
+      <c r="U17" t="s">
+        <v>37</v>
+      </c>
+      <c r="V17" t="s">
         <v>207</v>
       </c>
-      <c r="P13" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>217</v>
-      </c>
-      <c r="R13" t="s">
-        <v>218</v>
-      </c>
-      <c r="S13" t="s">
-        <v>219</v>
-      </c>
-      <c r="T13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>223</v>
-      </c>
-      <c r="B14" t="s">
-        <v>215</v>
-      </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J14" t="s">
-        <v>36</v>
-      </c>
-      <c r="K14" t="s">
-        <v>36</v>
-      </c>
-      <c r="L14" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" t="s">
-        <v>36</v>
-      </c>
-      <c r="N14" t="s">
-        <v>36</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="W17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>247</v>
+      </c>
+      <c r="B18" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" t="s">
+        <v>249</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" t="s">
+        <v>37</v>
+      </c>
+      <c r="L18" t="s">
+        <v>37</v>
+      </c>
+      <c r="M18" t="s">
+        <v>37</v>
+      </c>
+      <c r="N18" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18" t="s">
+        <v>37</v>
+      </c>
+      <c r="P18" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>37</v>
+      </c>
+      <c r="R18" t="s">
+        <v>37</v>
+      </c>
+      <c r="S18" t="s">
+        <v>37</v>
+      </c>
+      <c r="T18" t="s">
+        <v>37</v>
+      </c>
+      <c r="U18" t="s">
+        <v>37</v>
+      </c>
+      <c r="V18" t="s">
         <v>207</v>
       </c>
-      <c r="P14" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>225</v>
-      </c>
-      <c r="R14" t="s">
-        <v>218</v>
-      </c>
-      <c r="S14" t="s">
-        <v>219</v>
-      </c>
-      <c r="T14" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>227</v>
-      </c>
-      <c r="B15" t="s">
-        <v>215</v>
-      </c>
-      <c r="C15" t="s">
-        <v>228</v>
-      </c>
-      <c r="D15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" t="s">
-        <v>36</v>
-      </c>
-      <c r="J15" t="s">
-        <v>36</v>
-      </c>
-      <c r="K15" t="s">
-        <v>36</v>
-      </c>
-      <c r="L15" t="s">
-        <v>36</v>
-      </c>
-      <c r="M15" t="s">
-        <v>36</v>
-      </c>
-      <c r="N15" t="s">
-        <v>36</v>
-      </c>
-      <c r="O15" t="s">
+      <c r="W18" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B19" t="s">
+        <v>248</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" t="s">
+        <v>37</v>
+      </c>
+      <c r="J19" t="s">
+        <v>251</v>
+      </c>
+      <c r="K19" t="s">
+        <v>252</v>
+      </c>
+      <c r="L19" t="s">
+        <v>170</v>
+      </c>
+      <c r="M19" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" t="s">
+        <v>50</v>
+      </c>
+      <c r="O19" t="s">
+        <v>37</v>
+      </c>
+      <c r="P19" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>37</v>
+      </c>
+      <c r="R19" t="s">
+        <v>37</v>
+      </c>
+      <c r="S19" t="s">
+        <v>37</v>
+      </c>
+      <c r="T19" t="s">
+        <v>37</v>
+      </c>
+      <c r="U19" t="s">
+        <v>37</v>
+      </c>
+      <c r="V19" t="s">
         <v>207</v>
       </c>
-      <c r="P15" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>230</v>
-      </c>
-      <c r="R15" t="s">
-        <v>231</v>
-      </c>
-      <c r="S15" t="s">
-        <v>232</v>
-      </c>
-      <c r="T15" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B16" t="s">
-        <v>235</v>
-      </c>
-      <c r="C16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" t="s">
-        <v>206</v>
-      </c>
-      <c r="G16" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" t="s">
-        <v>236</v>
-      </c>
-      <c r="I16" t="s">
-        <v>237</v>
-      </c>
-      <c r="J16" t="s">
-        <v>36</v>
-      </c>
-      <c r="K16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L16" t="s">
-        <v>36</v>
-      </c>
-      <c r="M16" t="s">
-        <v>36</v>
-      </c>
-      <c r="N16" t="s">
-        <v>36</v>
-      </c>
-      <c r="O16" t="s">
-        <v>36</v>
-      </c>
-      <c r="P16" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>36</v>
-      </c>
-      <c r="R16" t="s">
-        <v>36</v>
-      </c>
-      <c r="S16" t="s">
-        <v>36</v>
-      </c>
-      <c r="T16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>238</v>
-      </c>
-      <c r="B17" t="s">
-        <v>235</v>
-      </c>
-      <c r="C17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" t="s">
-        <v>206</v>
-      </c>
-      <c r="G17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" t="s">
-        <v>239</v>
-      </c>
-      <c r="I17" t="s">
-        <v>237</v>
-      </c>
-      <c r="J17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M17" t="s">
-        <v>21</v>
-      </c>
-      <c r="N17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O17" t="s">
-        <v>36</v>
-      </c>
-      <c r="P17" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>36</v>
-      </c>
-      <c r="R17" t="s">
-        <v>36</v>
-      </c>
-      <c r="S17" t="s">
-        <v>36</v>
-      </c>
-      <c r="T17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>240</v>
-      </c>
-      <c r="B18" t="s">
-        <v>241</v>
-      </c>
-      <c r="C18" t="s">
-        <v>242</v>
-      </c>
-      <c r="D18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" t="s">
-        <v>36</v>
-      </c>
-      <c r="J18" t="s">
-        <v>36</v>
-      </c>
-      <c r="K18" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" t="s">
-        <v>36</v>
-      </c>
-      <c r="M18" t="s">
-        <v>36</v>
-      </c>
-      <c r="N18" t="s">
-        <v>36</v>
-      </c>
-      <c r="O18" t="s">
-        <v>36</v>
-      </c>
-      <c r="P18" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>36</v>
-      </c>
-      <c r="R18" t="s">
-        <v>36</v>
-      </c>
-      <c r="S18" t="s">
-        <v>36</v>
-      </c>
-      <c r="T18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>240</v>
-      </c>
-      <c r="B19" t="s">
-        <v>241</v>
-      </c>
-      <c r="C19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" t="s">
-        <v>244</v>
-      </c>
-      <c r="K19" t="s">
-        <v>245</v>
-      </c>
-      <c r="L19" t="s">
-        <v>167</v>
-      </c>
-      <c r="M19" t="s">
-        <v>36</v>
-      </c>
-      <c r="N19" t="s">
-        <v>49</v>
-      </c>
-      <c r="O19" t="s">
-        <v>36</v>
-      </c>
-      <c r="P19" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>36</v>
-      </c>
-      <c r="R19" t="s">
-        <v>36</v>
-      </c>
-      <c r="S19" t="s">
-        <v>36</v>
-      </c>
-      <c r="T19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="W19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B20" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C20" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T20" t="s">
+        <v>37</v>
+      </c>
+      <c r="U20" t="s">
+        <v>37</v>
+      </c>
+      <c r="V20" t="s">
+        <v>207</v>
+      </c>
+      <c r="W20" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>253</v>
+      </c>
+      <c r="B21" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>246</v>
-      </c>
-      <c r="B21" t="s">
-        <v>241</v>
-      </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J21" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="K21" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L21" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="U21" t="s">
+        <v>37</v>
+      </c>
+      <c r="V21" t="s">
+        <v>207</v>
+      </c>
+      <c r="W21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B22" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C22" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T22" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="U22" t="s">
+        <v>37</v>
+      </c>
+      <c r="V22" t="s">
+        <v>207</v>
+      </c>
+      <c r="W22" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C23" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T23" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="U23" t="s">
+        <v>37</v>
+      </c>
+      <c r="V23" t="s">
+        <v>207</v>
+      </c>
+      <c r="W23" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T24" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="U24" t="s">
+        <v>37</v>
+      </c>
+      <c r="V24" t="s">
+        <v>207</v>
+      </c>
+      <c r="W24" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -6587,122 +6899,122 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B4" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B5" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B6" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6710,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6730,19 +7042,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C8" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6750,19 +7062,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6770,33 +7082,33 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C10" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -6807,16 +7119,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B12" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C12" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -6827,16 +7139,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B13" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C13" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -6847,16 +7159,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -6867,16 +7179,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -6887,16 +7199,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -6907,16 +7219,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B17" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C17" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17">
         <v>13</v>
@@ -6927,16 +7239,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D18" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6962,90 +7274,90 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B3" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B7" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B8" t="s">
-        <v>299</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web/public/examples/example-with-constraint-rules.xlsx
+++ b/apps/web/public/examples/example-with-constraint-rules.xlsx
@@ -919,7 +919,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:51:36</t>
+    <t>12:17:43</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-with-constraint-rules.xlsx
+++ b/apps/web/public/examples/example-with-constraint-rules.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="307">
   <si>
     <t>Term</t>
   </si>
@@ -91,15 +91,81 @@
     <t>AMUS</t>
   </si>
   <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>MWF</t>
+  </si>
+  <si>
+    <t>14:45:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>SB 120</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>FA-Full</t>
+  </si>
+  <si>
+    <t>Musical Patterns II</t>
+  </si>
+  <si>
+    <t>Kim</t>
+  </si>
+  <si>
+    <t>Lecture</t>
+  </si>
+  <si>
+    <t>In-Person</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>UGRAD</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:05:00</t>
+  </si>
+  <si>
+    <t>SB 121</t>
+  </si>
+  <si>
+    <t>Gus Testwell</t>
+  </si>
+  <si>
+    <t>8:00 MWF is standard for the university but disallowed by this department's rule</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>09:15:00 - 10:20:00</t>
+  </si>
+  <si>
+    <t>NH 104</t>
+  </si>
+  <si>
+    <t>Discrete Rhythm</t>
+  </si>
+  <si>
+    <t>Cy Fictional</t>
+  </si>
+  <si>
     <t>228</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>TR</t>
   </si>
   <si>
@@ -109,39 +175,15 @@
     <t>NH 103</t>
   </si>
   <si>
-    <t>Full</t>
-  </si>
-  <si>
-    <t>FA-Full</t>
-  </si>
-  <si>
     <t>Harmonic Structures</t>
   </si>
   <si>
     <t>Ada Example</t>
   </si>
   <si>
-    <t>Lecture</t>
-  </si>
-  <si>
-    <t>In-Person</t>
-  </si>
-  <si>
     <t>Cohort course: clashes with BHAV 212 A</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>UGRAD</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>MWF</t>
-  </si>
-  <si>
     <t>11:00:00 - 12:05:00</t>
   </si>
   <si>
@@ -160,9 +202,6 @@
     <t>Multivoice Analysis</t>
   </si>
   <si>
-    <t>Cy Fictional</t>
-  </si>
-  <si>
     <t>241</t>
   </si>
   <si>
@@ -187,184 +226,175 @@
     <t>Not a standard time; allowed by this department's rule</t>
   </si>
   <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>09:15:00 - 10:20:00</t>
-  </si>
-  <si>
-    <t>NH 104</t>
-  </si>
-  <si>
-    <t>Discrete Rhythm</t>
-  </si>
-  <si>
-    <t>296</t>
+    <t>368</t>
+  </si>
+  <si>
+    <t>14:10:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>Corpus Studies I</t>
+  </si>
+  <si>
+    <t>Ben Sample</t>
+  </si>
+  <si>
+    <t>Runs into the colloquium hour (R 15:05)</t>
+  </si>
+  <si>
+    <t>375</t>
   </si>
   <si>
     <t>T</t>
   </si>
   <si>
-    <t>08:00:00 - 09:40:00</t>
-  </si>
-  <si>
-    <t>Introductory Harmonic Structures</t>
-  </si>
-  <si>
-    <t>Tuesday only: some of the days of TR at 8:00; allowed by this department's subset rule</t>
+    <t>Corpus Studies II</t>
+  </si>
+  <si>
+    <t>Tuesday only: some of the days of TR at 14:10; allowed by this department's subset rule</t>
+  </si>
+  <si>
+    <t>BHAV</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>NH 106</t>
+  </si>
+  <si>
+    <t>Introduction to Behavioral Dynamics</t>
+  </si>
+  <si>
+    <t>Lee</t>
+  </si>
+  <si>
+    <t>Lee's two sections are not back to back</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>10:30:00 - 11:35:00</t>
+  </si>
+  <si>
+    <t>NH 107</t>
+  </si>
+  <si>
+    <t>Dee Placeholder</t>
+  </si>
+  <si>
+    <t>10:30 is not a standard start (shown in orange)</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>HH 210</t>
+  </si>
+  <si>
+    <t>Behavior in Sport</t>
+  </si>
+  <si>
+    <t>Hal Fakename</t>
+  </si>
+  <si>
+    <t>There is no evening section yet</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:55:00</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>NH 105</t>
+  </si>
+  <si>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>Eli Specimen</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Stochastic Behavior</t>
+  </si>
+  <si>
+    <t>Same time as DIGI 318 A</t>
+  </si>
+  <si>
+    <t>DIGI</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>SB 110</t>
+  </si>
+  <si>
+    <t>Information Computing</t>
+  </si>
+  <si>
+    <t>Fay Mockson</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>13:30:00 - 14:35:00</t>
+  </si>
+  <si>
+    <t>Network Optimization</t>
+  </si>
+  <si>
+    <t>Kim teaches three in a row on MWF</t>
   </si>
   <si>
     <t>318</t>
   </si>
   <si>
-    <t>14:10:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>Corpus Studies I</t>
-  </si>
-  <si>
-    <t>Ben Sample</t>
-  </si>
-  <si>
-    <t>Runs into the colloquium hour (R 15:05)</t>
-  </si>
-  <si>
-    <t>BHAV</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>NH 106</t>
-  </si>
-  <si>
-    <t>Introduction to Behavioral Dynamics</t>
-  </si>
-  <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>Lee's two sections are not back to back</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>10:30:00 - 11:35:00</t>
-  </si>
-  <si>
-    <t>NH 107</t>
-  </si>
-  <si>
-    <t>Dee Placeholder</t>
-  </si>
-  <si>
-    <t>10:30 is not a standard start (shown in orange)</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>NH 105</t>
-  </si>
-  <si>
-    <t>Behavioral Methods</t>
-  </si>
-  <si>
-    <t>Eli Specimen</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Models of Change</t>
-  </si>
-  <si>
-    <t>226</t>
+    <t>Adaptive Systems</t>
+  </si>
+  <si>
+    <t>Same time as BHAV 312 A</t>
+  </si>
+  <si>
+    <t>325</t>
   </si>
   <si>
     <t>F</t>
   </si>
   <si>
-    <t>Applied Field Analysis</t>
-  </si>
-  <si>
-    <t>Friday only: some of the days of MWF at 9:15; not covered by the subset rule</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:55:00</t>
-  </si>
-  <si>
-    <t>Stochastic Behavior</t>
-  </si>
-  <si>
-    <t>Same time as DIGI 318 A</t>
-  </si>
-  <si>
-    <t>CRUD</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>14:45:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>SB 120</t>
-  </si>
-  <si>
-    <t>Introduction to Urban Systems</t>
-  </si>
-  <si>
-    <t>Kim</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:05:00</t>
-  </si>
-  <si>
-    <t>SB 121</t>
-  </si>
-  <si>
-    <t>Gus Testwell</t>
-  </si>
-  <si>
-    <t>8:00 MWF is standard for the university but disallowed by this department's rule</t>
-  </si>
-  <si>
-    <t>245</t>
-  </si>
-  <si>
-    <t>13:30:00 - 14:35:00</t>
-  </si>
-  <si>
-    <t>Urban Data Structures</t>
-  </si>
-  <si>
-    <t>Kim teaches three in a row on MWF</t>
-  </si>
-  <si>
-    <t>290</t>
+    <t>Information Capstone</t>
+  </si>
+  <si>
+    <t>Friday only: one of the days of MWF at 9:15; not covered by the subset rule</t>
+  </si>
+  <si>
+    <t>371</t>
   </si>
   <si>
     <t>SB 123</t>
   </si>
   <si>
-    <t>Urban Seminar</t>
-  </si>
-  <si>
-    <t>Hal Fakename</t>
-  </si>
-  <si>
-    <t>A seminar run as a 200- and a 300-level course: same instructor, room and time; allowed by this department's rule</t>
-  </si>
-  <si>
-    <t>CRUD 390 A</t>
-  </si>
-  <si>
-    <t>315</t>
+    <t>Information Ethics</t>
+  </si>
+  <si>
+    <t>A seminar run as a 300- and a 400-level course: same instructor, room and time; allowed by this department's rule</t>
+  </si>
+  <si>
+    <t>DIGI 471 A</t>
+  </si>
+  <si>
+    <t>378</t>
   </si>
   <si>
     <t>16:00:00 - 17:00:00</t>
@@ -373,55 +403,19 @@
     <t>SB 122</t>
   </si>
   <si>
-    <t>Planning Algorithms</t>
-  </si>
-  <si>
-    <t>390</t>
+    <t>Information Visualization</t>
+  </si>
+  <si>
+    <t>471</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>The 300-level listing of the seminar; its load is counted with CRUD 290</t>
-  </si>
-  <si>
-    <t>CRUD 290 A</t>
-  </si>
-  <si>
-    <t>DIGI</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>SB 110</t>
-  </si>
-  <si>
-    <t>Information Computing</t>
-  </si>
-  <si>
-    <t>Fay Mockson</t>
-  </si>
-  <si>
-    <t>Digital Information Topics</t>
-  </si>
-  <si>
-    <t>Same time as BHAV 312 A</t>
-  </si>
-  <si>
-    <t>HELP</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>HH 210</t>
-  </si>
-  <si>
-    <t>Ecology Core</t>
-  </si>
-  <si>
-    <t>There is no evening section yet</t>
+    <t>The 400-level listing of the seminar; its load is counted with DIGI 371</t>
+  </si>
+  <si>
+    <t>DIGI 371 A</t>
   </si>
   <si>
     <t>SectionId</t>
@@ -478,7 +472,7 @@
     <t>AY25-FA-BHAV212-A</t>
   </si>
   <si>
-    <t>AY25-FA-AMUS261-A</t>
+    <t>AY25-FA-AMUS203-A</t>
   </si>
   <si>
     <t>09:15</t>
@@ -496,31 +490,31 @@
     <t>AY25-FA-BHAV312-A</t>
   </si>
   <si>
-    <t>AY25-FA-CRUD245-A</t>
+    <t>AY25-FA-DIGI306-A</t>
   </si>
   <si>
     <t>13:30</t>
   </si>
   <si>
-    <t>AY25-FA-CRUD167-A</t>
+    <t>AY25-FA-AMUS145-A</t>
   </si>
   <si>
     <t>14:45</t>
   </si>
   <si>
-    <t>AY25-FA-CRUD315-A</t>
+    <t>AY25-FA-DIGI378-A</t>
   </si>
   <si>
     <t>16:00</t>
   </si>
   <si>
-    <t>AY25-FA-CRUD167-B</t>
+    <t>AY25-FA-AMUS145-B</t>
   </si>
   <si>
     <t>08:00</t>
   </si>
   <si>
-    <t>AY25-FA-AMUS318-A</t>
+    <t>AY25-FA-AMUS368-A</t>
   </si>
   <si>
     <t>14:10</t>
@@ -544,10 +538,10 @@
     <t>10:30</t>
   </si>
   <si>
-    <t>AY25-FA-HELP111-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-HELP111-B</t>
+    <t>AY25-FA-BHAV121-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV121-B</t>
   </si>
   <si>
     <t>AY25-SP-AMUS235-A</t>
@@ -556,16 +550,16 @@
     <t>AY25-SP-BHAV219-A</t>
   </si>
   <si>
-    <t>AY25-SP-AMUS296-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-BHAV226-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-CRUD290-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-CRUD390-A</t>
+    <t>AY25-SP-AMUS375-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI325-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI371-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI471-A</t>
   </si>
   <si>
     <t>Activity</t>
@@ -649,7 +643,7 @@
     <t>BHAV 212</t>
   </si>
   <si>
-    <t>AMUS 261</t>
+    <t>AMUS 203</t>
   </si>
   <si>
     <t>Digital information minor: any two electives</t>
@@ -670,7 +664,7 @@
     <t>BHAV 312</t>
   </si>
   <si>
-    <t>CRUD 245</t>
+    <t>DIGI 306</t>
   </si>
   <si>
     <t>Digital information minor: some pair of electives</t>
@@ -721,10 +715,10 @@
     <t>A rule about an instructor instead of courses.</t>
   </si>
   <si>
-    <t>Ecology Core needs an evening section</t>
-  </si>
-  <si>
-    <t>HELP 111</t>
+    <t>Behavior in Sport needs an evening section</t>
+  </si>
+  <si>
+    <t>BHAV 121</t>
   </si>
   <si>
     <t>17:00</t>
@@ -793,16 +787,16 @@
     <t>65</t>
   </si>
   <si>
-    <t>Harmonic structures may meet one day of TR</t>
+    <t>Corpus studies may meet one day of TR</t>
   </si>
   <si>
     <t>subset</t>
   </si>
   <si>
-    <t>AMUS 296</t>
-  </si>
-  <si>
-    <t>AMUS 296 is meant to meet on only one of the standard days, so it is not flagged for that.</t>
+    <t>AMUS 375</t>
+  </si>
+  <si>
+    <t>AMUS 375 is meant to meet on only one of the standard days, so it is not flagged for that.</t>
   </si>
   <si>
     <t>The seminar runs at two levels</t>
@@ -811,13 +805,13 @@
     <t>colocate</t>
   </si>
   <si>
-    <t>CRUD 290</t>
-  </si>
-  <si>
-    <t>CRUD 290 and CRUD 390 are one class, so they share an instructor, a room and a time on purpose.</t>
-  </si>
-  <si>
-    <t>CRUD 390</t>
+    <t>DIGI 371</t>
+  </si>
+  <si>
+    <t>DIGI 371 and DIGI 471 are one class, so they share an instructor, a room and a time on purpose.</t>
+  </si>
+  <si>
+    <t>DIGI 471</t>
   </si>
   <si>
     <t>Kind</t>
@@ -919,7 +913,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>12:17:43</t>
+    <t>14:23:18</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -1451,7 +1445,7 @@
         <v>31</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M2" t="s">
         <v>32</v>
@@ -1469,19 +1463,19 @@
         <v>36</v>
       </c>
       <c r="R2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s">
         <v>37</v>
       </c>
-      <c r="S2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" t="s">
-        <v>37</v>
-      </c>
-      <c r="U2" t="s">
-        <v>38</v>
-      </c>
       <c r="V2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -1495,7 +1489,7 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>26</v>
@@ -1504,13 +1498,13 @@
         <v>26</v>
       </c>
       <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" t="s">
         <v>40</v>
-      </c>
-      <c r="H3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" t="s">
-        <v>29</v>
       </c>
       <c r="J3" t="s">
         <v>30</v>
@@ -1525,7 +1519,7 @@
         <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="O3" t="s">
         <v>34</v>
@@ -1537,30 +1531,30 @@
         <v>42</v>
       </c>
       <c r="R3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" t="s">
         <v>37</v>
       </c>
-      <c r="S3" t="s">
-        <v>37</v>
-      </c>
-      <c r="T3" t="s">
-        <v>37</v>
-      </c>
-      <c r="U3" t="s">
-        <v>38</v>
-      </c>
       <c r="V3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -1575,19 +1569,19 @@
         <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="J4" t="s">
         <v>30</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M4" t="s">
         <v>46</v>
@@ -1602,22 +1596,22 @@
         <v>35</v>
       </c>
       <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" t="s">
         <v>37</v>
       </c>
-      <c r="R4" t="s">
-        <v>37</v>
-      </c>
-      <c r="S4" t="s">
-        <v>37</v>
-      </c>
-      <c r="T4" t="s">
-        <v>37</v>
-      </c>
-      <c r="U4" t="s">
-        <v>38</v>
-      </c>
       <c r="V4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -1634,19 +1628,19 @@
         <v>25</v>
       </c>
       <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
         <v>49</v>
       </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>50</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>51</v>
-      </c>
-      <c r="I5" t="s">
-        <v>52</v>
       </c>
       <c r="J5" t="s">
         <v>30</v>
@@ -1655,37 +1649,37 @@
         <v>31</v>
       </c>
       <c r="L5">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" t="s">
         <v>53</v>
       </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
       <c r="O5" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="P5" t="s">
         <v>35</v>
       </c>
       <c r="Q5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R5" t="s">
+        <v>36</v>
+      </c>
+      <c r="S5" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" t="s">
+        <v>36</v>
+      </c>
+      <c r="U5" t="s">
         <v>37</v>
       </c>
-      <c r="S5" t="s">
-        <v>37</v>
-      </c>
-      <c r="T5" t="s">
-        <v>37</v>
-      </c>
-      <c r="U5" t="s">
-        <v>38</v>
-      </c>
       <c r="V5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -1696,10 +1690,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
@@ -1708,13 +1702,13 @@
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J6" t="s">
         <v>30</v>
@@ -1726,10 +1720,10 @@
         <v>65</v>
       </c>
       <c r="M6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="O6" t="s">
         <v>34</v>
@@ -1738,33 +1732,33 @@
         <v>35</v>
       </c>
       <c r="Q6" t="s">
+        <v>56</v>
+      </c>
+      <c r="R6" t="s">
+        <v>36</v>
+      </c>
+      <c r="S6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U6" t="s">
         <v>37</v>
       </c>
-      <c r="R6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S6" t="s">
-        <v>37</v>
-      </c>
-      <c r="T6" t="s">
-        <v>37</v>
-      </c>
-      <c r="U6" t="s">
-        <v>38</v>
-      </c>
       <c r="V6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
@@ -1776,25 +1770,25 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="J7" t="s">
         <v>30</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N7" t="s">
         <v>47</v>
@@ -1806,22 +1800,22 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="R7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S7" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" t="s">
+        <v>36</v>
+      </c>
+      <c r="U7" t="s">
         <v>37</v>
       </c>
-      <c r="S7" t="s">
-        <v>37</v>
-      </c>
-      <c r="T7" t="s">
-        <v>37</v>
-      </c>
-      <c r="U7" t="s">
-        <v>38</v>
-      </c>
       <c r="V7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -1832,25 +1826,25 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J8" t="s">
         <v>30</v>
@@ -1859,37 +1853,37 @@
         <v>31</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M8" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" t="s">
+        <v>53</v>
+      </c>
+      <c r="O8" t="s">
         <v>67</v>
-      </c>
-      <c r="N8" t="s">
-        <v>68</v>
-      </c>
-      <c r="O8" t="s">
-        <v>34</v>
       </c>
       <c r="P8" t="s">
         <v>35</v>
       </c>
       <c r="Q8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" t="s">
+        <v>36</v>
+      </c>
+      <c r="U8" t="s">
         <v>37</v>
       </c>
-      <c r="S8" t="s">
-        <v>37</v>
-      </c>
-      <c r="T8" t="s">
-        <v>37</v>
-      </c>
-      <c r="U8" t="s">
-        <v>38</v>
-      </c>
       <c r="V8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -1897,10 +1891,10 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
@@ -1912,13 +1906,13 @@
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I9" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="J9" t="s">
         <v>30</v>
@@ -1927,13 +1921,13 @@
         <v>31</v>
       </c>
       <c r="L9">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O9" t="s">
         <v>34</v>
@@ -1942,36 +1936,36 @@
         <v>35</v>
       </c>
       <c r="Q9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U9" t="s">
         <v>37</v>
       </c>
-      <c r="S9" t="s">
-        <v>37</v>
-      </c>
-      <c r="T9" t="s">
-        <v>37</v>
-      </c>
-      <c r="U9" t="s">
-        <v>38</v>
-      </c>
       <c r="V9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
         <v>26</v>
@@ -1980,28 +1974,28 @@
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="J10" t="s">
         <v>30</v>
       </c>
       <c r="K10" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="L10">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N10" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="O10" t="s">
         <v>34</v>
@@ -2010,22 +2004,22 @@
         <v>35</v>
       </c>
       <c r="Q10" t="s">
+        <v>77</v>
+      </c>
+      <c r="R10" t="s">
+        <v>36</v>
+      </c>
+      <c r="S10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" t="s">
+        <v>36</v>
+      </c>
+      <c r="U10" t="s">
         <v>37</v>
       </c>
-      <c r="R10" t="s">
-        <v>37</v>
-      </c>
-      <c r="S10" t="s">
-        <v>37</v>
-      </c>
-      <c r="T10" t="s">
-        <v>37</v>
-      </c>
-      <c r="U10" t="s">
-        <v>38</v>
-      </c>
       <c r="V10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -2033,13 +2027,13 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
         <v>26</v>
@@ -2048,13 +2042,13 @@
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="I11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J11" t="s">
         <v>30</v>
@@ -2066,10 +2060,10 @@
         <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="N11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O11" t="s">
         <v>34</v>
@@ -2078,22 +2072,22 @@
         <v>35</v>
       </c>
       <c r="Q11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R11" t="s">
+        <v>36</v>
+      </c>
+      <c r="S11" t="s">
+        <v>36</v>
+      </c>
+      <c r="T11" t="s">
+        <v>36</v>
+      </c>
+      <c r="U11" t="s">
         <v>37</v>
       </c>
-      <c r="S11" t="s">
-        <v>37</v>
-      </c>
-      <c r="T11" t="s">
-        <v>37</v>
-      </c>
-      <c r="U11" t="s">
-        <v>38</v>
-      </c>
       <c r="V11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -2101,13 +2095,13 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>26</v>
@@ -2119,10 +2113,10 @@
         <v>27</v>
       </c>
       <c r="H12" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="I12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J12" t="s">
         <v>30</v>
@@ -2131,13 +2125,13 @@
         <v>31</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O12" t="s">
         <v>34</v>
@@ -2146,36 +2140,36 @@
         <v>35</v>
       </c>
       <c r="Q12" t="s">
+        <v>36</v>
+      </c>
+      <c r="R12" t="s">
+        <v>36</v>
+      </c>
+      <c r="S12" t="s">
+        <v>36</v>
+      </c>
+      <c r="T12" t="s">
+        <v>36</v>
+      </c>
+      <c r="U12" t="s">
         <v>37</v>
       </c>
-      <c r="R12" t="s">
-        <v>37</v>
-      </c>
-      <c r="S12" t="s">
-        <v>37</v>
-      </c>
-      <c r="T12" t="s">
-        <v>37</v>
-      </c>
-      <c r="U12" t="s">
-        <v>38</v>
-      </c>
       <c r="V12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
         <v>26</v>
@@ -2187,25 +2181,25 @@
         <v>27</v>
       </c>
       <c r="H13" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s">
         <v>30</v>
       </c>
       <c r="K13" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M13" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="N13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="O13" t="s">
         <v>34</v>
@@ -2214,33 +2208,33 @@
         <v>35</v>
       </c>
       <c r="Q13" t="s">
+        <v>88</v>
+      </c>
+      <c r="R13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S13" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" t="s">
+        <v>36</v>
+      </c>
+      <c r="U13" t="s">
         <v>37</v>
       </c>
-      <c r="R13" t="s">
-        <v>37</v>
-      </c>
-      <c r="S13" t="s">
-        <v>37</v>
-      </c>
-      <c r="T13" t="s">
-        <v>37</v>
-      </c>
-      <c r="U13" t="s">
-        <v>38</v>
-      </c>
       <c r="V13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
         <v>25</v>
@@ -2252,28 +2246,28 @@
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="I14" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s">
         <v>30</v>
       </c>
       <c r="K14" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L14">
         <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N14" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="O14" t="s">
         <v>34</v>
@@ -2282,22 +2276,22 @@
         <v>35</v>
       </c>
       <c r="Q14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="R14" t="s">
+        <v>36</v>
+      </c>
+      <c r="S14" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" t="s">
+        <v>36</v>
+      </c>
+      <c r="U14" t="s">
         <v>37</v>
       </c>
-      <c r="S14" t="s">
-        <v>37</v>
-      </c>
-      <c r="T14" t="s">
-        <v>37</v>
-      </c>
-      <c r="U14" t="s">
-        <v>38</v>
-      </c>
       <c r="V14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -2305,13 +2299,13 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
         <v>26</v>
@@ -2320,13 +2314,13 @@
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I15" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J15" t="s">
         <v>30</v>
@@ -2338,10 +2332,10 @@
         <v>100</v>
       </c>
       <c r="M15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N15" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="O15" t="s">
         <v>34</v>
@@ -2350,22 +2344,22 @@
         <v>35</v>
       </c>
       <c r="Q15" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="R15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S15" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" t="s">
+        <v>36</v>
+      </c>
+      <c r="U15" t="s">
         <v>37</v>
       </c>
-      <c r="S15" t="s">
-        <v>37</v>
-      </c>
-      <c r="T15" t="s">
-        <v>37</v>
-      </c>
-      <c r="U15" t="s">
-        <v>38</v>
-      </c>
       <c r="V15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -2373,10 +2367,10 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" t="s">
         <v>95</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
       </c>
       <c r="D16" t="s">
         <v>25</v>
@@ -2388,13 +2382,13 @@
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="I16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J16" t="s">
         <v>30</v>
@@ -2403,13 +2397,13 @@
         <v>31</v>
       </c>
       <c r="L16">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O16" t="s">
         <v>34</v>
@@ -2418,36 +2412,36 @@
         <v>35</v>
       </c>
       <c r="Q16" t="s">
+        <v>36</v>
+      </c>
+      <c r="R16" t="s">
+        <v>36</v>
+      </c>
+      <c r="S16" t="s">
+        <v>36</v>
+      </c>
+      <c r="T16" t="s">
+        <v>36</v>
+      </c>
+      <c r="U16" t="s">
         <v>37</v>
       </c>
-      <c r="R16" t="s">
-        <v>37</v>
-      </c>
-      <c r="S16" t="s">
-        <v>37</v>
-      </c>
-      <c r="T16" t="s">
-        <v>37</v>
-      </c>
-      <c r="U16" t="s">
-        <v>38</v>
-      </c>
       <c r="V16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
         <v>26</v>
@@ -2456,28 +2450,28 @@
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H17" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="I17" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J17" t="s">
         <v>30</v>
       </c>
       <c r="K17" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="L17">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N17" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O17" t="s">
         <v>34</v>
@@ -2486,22 +2480,22 @@
         <v>35</v>
       </c>
       <c r="Q17" t="s">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="R17" t="s">
+        <v>36</v>
+      </c>
+      <c r="S17" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" t="s">
+        <v>36</v>
+      </c>
+      <c r="U17" t="s">
         <v>37</v>
       </c>
-      <c r="S17" t="s">
-        <v>37</v>
-      </c>
-      <c r="T17" t="s">
-        <v>37</v>
-      </c>
-      <c r="U17" t="s">
-        <v>38</v>
-      </c>
       <c r="V17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -2509,10 +2503,10 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
         <v>25</v>
@@ -2524,13 +2518,13 @@
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H18" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="I18" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J18" t="s">
         <v>30</v>
@@ -2539,13 +2533,13 @@
         <v>31</v>
       </c>
       <c r="L18">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="N18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O18" t="s">
         <v>34</v>
@@ -2554,22 +2548,22 @@
         <v>35</v>
       </c>
       <c r="Q18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="R18" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" t="s">
+        <v>36</v>
+      </c>
+      <c r="U18" t="s">
         <v>37</v>
       </c>
-      <c r="S18" t="s">
-        <v>37</v>
-      </c>
-      <c r="T18" t="s">
-        <v>37</v>
-      </c>
-      <c r="U18" t="s">
-        <v>38</v>
-      </c>
       <c r="V18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -2577,10 +2571,10 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
         <v>25</v>
@@ -2595,10 +2589,10 @@
         <v>27</v>
       </c>
       <c r="H19" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="I19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J19" t="s">
         <v>30</v>
@@ -2607,13 +2601,13 @@
         <v>31</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M19" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="N19" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="O19" t="s">
         <v>34</v>
@@ -2622,22 +2616,22 @@
         <v>35</v>
       </c>
       <c r="Q19" t="s">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="R19" t="s">
+        <v>36</v>
+      </c>
+      <c r="S19" t="s">
+        <v>36</v>
+      </c>
+      <c r="T19" t="s">
+        <v>36</v>
+      </c>
+      <c r="U19" t="s">
         <v>37</v>
       </c>
-      <c r="S19" t="s">
-        <v>37</v>
-      </c>
-      <c r="T19" t="s">
-        <v>37</v>
-      </c>
-      <c r="U19" t="s">
-        <v>38</v>
-      </c>
       <c r="V19" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -2645,10 +2639,10 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
         <v>25</v>
@@ -2660,13 +2654,13 @@
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="I20" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="J20" t="s">
         <v>30</v>
@@ -2675,13 +2669,13 @@
         <v>31</v>
       </c>
       <c r="L20">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M20" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="N20" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="O20" t="s">
         <v>34</v>
@@ -2690,22 +2684,22 @@
         <v>35</v>
       </c>
       <c r="Q20" t="s">
+        <v>112</v>
+      </c>
+      <c r="R20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S20" t="s">
+        <v>36</v>
+      </c>
+      <c r="T20" t="s">
+        <v>36</v>
+      </c>
+      <c r="U20" t="s">
         <v>37</v>
       </c>
-      <c r="R20" t="s">
-        <v>37</v>
-      </c>
-      <c r="S20" t="s">
-        <v>37</v>
-      </c>
-      <c r="T20" t="s">
-        <v>37</v>
-      </c>
-      <c r="U20" t="s">
-        <v>38</v>
-      </c>
       <c r="V20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -2713,10 +2707,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
@@ -2725,16 +2719,16 @@
         <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H21" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I21" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="J21" t="s">
         <v>30</v>
@@ -2746,10 +2740,10 @@
         <v>100</v>
       </c>
       <c r="M21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N21" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="O21" t="s">
         <v>34</v>
@@ -2758,33 +2752,33 @@
         <v>35</v>
       </c>
       <c r="Q21" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="R21" t="s">
+        <v>36</v>
+      </c>
+      <c r="S21" t="s">
+        <v>36</v>
+      </c>
+      <c r="T21" t="s">
+        <v>36</v>
+      </c>
+      <c r="U21" t="s">
         <v>37</v>
       </c>
-      <c r="S21" t="s">
-        <v>37</v>
-      </c>
-      <c r="T21" t="s">
-        <v>37</v>
-      </c>
-      <c r="U21" t="s">
-        <v>38</v>
-      </c>
       <c r="V21" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
         <v>25</v>
@@ -2796,28 +2790,28 @@
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="H22" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I22" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="J22" t="s">
         <v>30</v>
       </c>
       <c r="K22" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="L22">
         <v>65</v>
       </c>
       <c r="M22" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N22" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="O22" t="s">
         <v>34</v>
@@ -2826,22 +2820,22 @@
         <v>35</v>
       </c>
       <c r="Q22" t="s">
+        <v>119</v>
+      </c>
+      <c r="R22" t="s">
+        <v>36</v>
+      </c>
+      <c r="S22" t="s">
+        <v>36</v>
+      </c>
+      <c r="T22" t="s">
+        <v>36</v>
+      </c>
+      <c r="U22" t="s">
         <v>37</v>
       </c>
-      <c r="R22" t="s">
-        <v>37</v>
-      </c>
-      <c r="S22" t="s">
-        <v>37</v>
-      </c>
-      <c r="T22" t="s">
-        <v>37</v>
-      </c>
-      <c r="U22" t="s">
-        <v>38</v>
-      </c>
       <c r="V22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
@@ -2849,10 +2843,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
         <v>25</v>
@@ -2864,13 +2858,13 @@
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H23" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="I23" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="J23" t="s">
         <v>30</v>
@@ -2882,10 +2876,10 @@
         <v>100</v>
       </c>
       <c r="M23" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="N23" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="O23" t="s">
         <v>34</v>
@@ -2894,22 +2888,22 @@
         <v>35</v>
       </c>
       <c r="Q23" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="R23" t="s">
+        <v>36</v>
+      </c>
+      <c r="S23" t="s">
+        <v>36</v>
+      </c>
+      <c r="T23" t="s">
+        <v>36</v>
+      </c>
+      <c r="U23" t="s">
         <v>37</v>
       </c>
-      <c r="S23" t="s">
-        <v>37</v>
-      </c>
-      <c r="T23" t="s">
-        <v>37</v>
-      </c>
-      <c r="U23" t="s">
-        <v>38</v>
-      </c>
       <c r="V23" t="s">
-        <v>37</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
@@ -2917,10 +2911,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
         <v>25</v>
@@ -2932,13 +2926,13 @@
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="H24" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="I24" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J24" t="s">
         <v>30</v>
@@ -2947,13 +2941,13 @@
         <v>31</v>
       </c>
       <c r="L24">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M24" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="N24" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="O24" t="s">
         <v>34</v>
@@ -2962,22 +2956,22 @@
         <v>35</v>
       </c>
       <c r="Q24" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="R24" t="s">
+        <v>36</v>
+      </c>
+      <c r="S24" t="s">
+        <v>36</v>
+      </c>
+      <c r="T24" t="s">
+        <v>36</v>
+      </c>
+      <c r="U24" t="s">
         <v>37</v>
       </c>
-      <c r="S24" t="s">
-        <v>37</v>
-      </c>
-      <c r="T24" t="s">
-        <v>37</v>
-      </c>
-      <c r="U24" t="s">
-        <v>38</v>
-      </c>
       <c r="V24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
@@ -2985,28 +2979,28 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
         <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H25" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="I25" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J25" t="s">
         <v>30</v>
@@ -3018,10 +3012,10 @@
         <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="N25" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="O25" t="s">
         <v>34</v>
@@ -3030,22 +3024,22 @@
         <v>35</v>
       </c>
       <c r="Q25" t="s">
+        <v>131</v>
+      </c>
+      <c r="R25" t="s">
+        <v>36</v>
+      </c>
+      <c r="S25" t="s">
+        <v>36</v>
+      </c>
+      <c r="T25" t="s">
+        <v>36</v>
+      </c>
+      <c r="U25" t="s">
         <v>37</v>
       </c>
-      <c r="R25" t="s">
-        <v>37</v>
-      </c>
-      <c r="S25" t="s">
-        <v>37</v>
-      </c>
-      <c r="T25" t="s">
-        <v>37</v>
-      </c>
-      <c r="U25" t="s">
-        <v>38</v>
-      </c>
       <c r="V25" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -3086,13 +3080,13 @@
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -3116,22 +3110,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -3140,10 +3134,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -3152,10 +3146,10 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>18</v>
@@ -3166,13 +3160,13 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
         <v>22</v>
@@ -3184,13 +3178,13 @@
         <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H2" t="s">
         <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -3199,60 +3193,60 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O2">
         <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="Q2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="R2" t="s">
         <v>34</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U2" t="s">
         <v>35</v>
       </c>
       <c r="V2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="W2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -3264,13 +3258,13 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -3279,60 +3273,60 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O3">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="Q3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="R3" t="s">
         <v>34</v>
       </c>
       <c r="S3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U3" t="s">
         <v>35</v>
       </c>
       <c r="V3" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -3341,16 +3335,16 @@
         <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -3359,60 +3353,60 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="Q4" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="R4" t="s">
         <v>34</v>
       </c>
       <c r="S4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U4" t="s">
         <v>35</v>
       </c>
       <c r="V4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -3424,7 +3418,7 @@
         <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -3439,60 +3433,60 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O5">
         <v>65</v>
       </c>
       <c r="P5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="R5" t="s">
         <v>34</v>
       </c>
       <c r="S5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U5" t="s">
         <v>35</v>
       </c>
       <c r="V5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -3501,16 +3495,16 @@
         <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="H6" t="s">
         <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3519,60 +3513,60 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="Q6" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="R6" t="s">
         <v>34</v>
       </c>
       <c r="S6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U6" t="s">
         <v>35</v>
       </c>
       <c r="V6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -3581,16 +3575,16 @@
         <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="G7" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="H7" t="s">
         <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3599,60 +3593,60 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="R7" t="s">
         <v>34</v>
       </c>
       <c r="S7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U7" t="s">
         <v>35</v>
       </c>
       <c r="V7" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="W7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -3661,16 +3655,16 @@
         <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="H8" t="s">
         <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3679,60 +3673,60 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M8" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="Q8" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="R8" t="s">
         <v>34</v>
       </c>
       <c r="S8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U8" t="s">
         <v>35</v>
       </c>
       <c r="V8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="W8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -3741,16 +3735,16 @@
         <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H9" t="s">
         <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -3759,60 +3753,60 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M9" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O9">
         <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="Q9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="R9" t="s">
         <v>34</v>
       </c>
       <c r="S9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U9" t="s">
         <v>35</v>
       </c>
       <c r="V9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="W9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -3821,16 +3815,16 @@
         <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="H10" t="s">
         <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3839,60 +3833,60 @@
         <v>4</v>
       </c>
       <c r="L10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M10" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O10">
         <v>65</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="Q10" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="R10" t="s">
         <v>34</v>
       </c>
       <c r="S10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U10" t="s">
         <v>35</v>
       </c>
       <c r="V10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
@@ -3901,16 +3895,16 @@
         <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H11" t="s">
         <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3919,60 +3913,60 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M11" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O11">
         <v>60</v>
       </c>
       <c r="P11" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="Q11" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="R11" t="s">
         <v>34</v>
       </c>
       <c r="S11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U11" t="s">
         <v>35</v>
       </c>
       <c r="V11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
@@ -3981,16 +3975,16 @@
         <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I12" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -3999,60 +3993,60 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O12">
         <v>65</v>
       </c>
       <c r="P12" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="Q12" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="R12" t="s">
         <v>34</v>
       </c>
       <c r="S12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U12" t="s">
         <v>35</v>
       </c>
       <c r="V12" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="W12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -4064,13 +4058,13 @@
         <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H13" t="s">
         <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -4079,60 +4073,60 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M13" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="Q13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="R13" t="s">
         <v>34</v>
       </c>
       <c r="S13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U13" t="s">
         <v>35</v>
       </c>
       <c r="V13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="W13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
@@ -4144,13 +4138,13 @@
         <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H14" t="s">
         <v>25</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -4159,60 +4153,60 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M14" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="N14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O14">
         <v>50</v>
       </c>
       <c r="P14" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="Q14" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="R14" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="S14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U14" t="s">
         <v>35</v>
       </c>
       <c r="V14" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="W14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
@@ -4221,16 +4215,16 @@
         <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s">
         <v>25</v>
       </c>
       <c r="I15" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4239,60 +4233,60 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M15" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O15">
         <v>65</v>
       </c>
       <c r="P15" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="R15" t="s">
         <v>34</v>
       </c>
       <c r="S15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U15" t="s">
         <v>35</v>
       </c>
       <c r="V15" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="W15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
@@ -4301,16 +4295,16 @@
         <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I16" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -4319,60 +4313,60 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M16" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O16">
         <v>65</v>
       </c>
       <c r="P16" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="R16" t="s">
         <v>34</v>
       </c>
       <c r="S16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U16" t="s">
         <v>35</v>
       </c>
       <c r="V16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
@@ -4381,16 +4375,16 @@
         <v>30</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -4399,60 +4393,60 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M17" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O17">
         <v>65</v>
       </c>
       <c r="P17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="Q17" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="R17" t="s">
         <v>34</v>
       </c>
       <c r="S17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U17" t="s">
         <v>35</v>
       </c>
       <c r="V17" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="W17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D18" t="s">
         <v>22</v>
@@ -4461,16 +4455,16 @@
         <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s">
         <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -4479,60 +4473,60 @@
         <v>4</v>
       </c>
       <c r="L18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M18" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O18">
         <v>65</v>
       </c>
       <c r="P18" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="R18" t="s">
         <v>34</v>
       </c>
       <c r="S18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U18" t="s">
         <v>35</v>
       </c>
       <c r="V18" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="W18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
@@ -4541,16 +4535,16 @@
         <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I19" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -4559,63 +4553,63 @@
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M19" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N19" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="Q19" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="R19" t="s">
         <v>34</v>
       </c>
       <c r="S19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U19" t="s">
         <v>35</v>
       </c>
       <c r="V19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
@@ -4624,7 +4618,7 @@
         <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="H20" t="s">
         <v>25</v>
@@ -4639,78 +4633,78 @@
         <v>4</v>
       </c>
       <c r="L20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M20" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="Q20" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="R20" t="s">
         <v>34</v>
       </c>
       <c r="S20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U20" t="s">
         <v>35</v>
       </c>
       <c r="V20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
         <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="H21" t="s">
         <v>25</v>
       </c>
       <c r="I21" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -4719,63 +4713,63 @@
         <v>4</v>
       </c>
       <c r="L21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M21" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="Q21" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="R21" t="s">
         <v>34</v>
       </c>
       <c r="S21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U21" t="s">
         <v>35</v>
       </c>
       <c r="V21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s">
         <v>30</v>
@@ -4784,7 +4778,7 @@
         <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H22" t="s">
         <v>25</v>
@@ -4799,10 +4793,10 @@
         <v>4</v>
       </c>
       <c r="L22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M22" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="N22" t="s">
         <v>166</v>
@@ -4811,66 +4805,66 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="Q22" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="R22" t="s">
         <v>34</v>
       </c>
       <c r="S22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U22" t="s">
         <v>35</v>
       </c>
       <c r="V22" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="W22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
         <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="H23" t="s">
         <v>25</v>
       </c>
       <c r="I23" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -4879,60 +4873,60 @@
         <v>4</v>
       </c>
       <c r="L23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M23" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="N23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O23">
         <v>65</v>
       </c>
       <c r="P23" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="Q23" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="R23" t="s">
         <v>34</v>
       </c>
       <c r="S23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U23" t="s">
         <v>35</v>
       </c>
       <c r="V23" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="W23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
@@ -4941,16 +4935,16 @@
         <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="H24" t="s">
         <v>25</v>
       </c>
       <c r="I24" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -4959,60 +4953,60 @@
         <v>4</v>
       </c>
       <c r="L24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M24" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="Q24" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="R24" t="s">
         <v>34</v>
       </c>
       <c r="S24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U24" t="s">
         <v>35</v>
       </c>
       <c r="V24" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="W24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
@@ -5021,16 +5015,16 @@
         <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G25" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="H25" t="s">
         <v>25</v>
       </c>
       <c r="I25" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -5039,49 +5033,49 @@
         <v>4</v>
       </c>
       <c r="L25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M25" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N25" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="Q25" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="R25" t="s">
         <v>34</v>
       </c>
       <c r="S25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U25" t="s">
         <v>35</v>
       </c>
       <c r="V25" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="W25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -5102,7 +5096,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5129,19 +5123,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -5178,70 +5172,70 @@
   <sheetData>
     <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>16</v>
@@ -5249,1635 +5243,1635 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" t="s">
         <v>204</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" t="s">
         <v>205</v>
       </c>
-      <c r="C2" t="s">
+      <c r="W2" t="s">
         <v>206</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" t="s">
-        <v>37</v>
-      </c>
-      <c r="U2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" t="s">
-        <v>207</v>
-      </c>
-      <c r="W2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V3" t="s">
         <v>205</v>
       </c>
-      <c r="C3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" t="s">
-        <v>37</v>
-      </c>
-      <c r="S3" t="s">
-        <v>37</v>
-      </c>
-      <c r="T3" t="s">
-        <v>37</v>
-      </c>
-      <c r="U3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V3" t="s">
-        <v>207</v>
-      </c>
       <c r="W3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" t="s">
         <v>205</v>
       </c>
-      <c r="C4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O4" t="s">
-        <v>37</v>
-      </c>
-      <c r="P4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R4" t="s">
-        <v>37</v>
-      </c>
-      <c r="S4" t="s">
-        <v>37</v>
-      </c>
-      <c r="T4" t="s">
-        <v>37</v>
-      </c>
-      <c r="U4" t="s">
-        <v>37</v>
-      </c>
-      <c r="V4" t="s">
-        <v>207</v>
-      </c>
       <c r="W4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
         <v>211</v>
       </c>
-      <c r="B5" t="s">
+      <c r="G5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" t="s">
+        <v>36</v>
+      </c>
+      <c r="S5" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" t="s">
+        <v>36</v>
+      </c>
+      <c r="U5" t="s">
+        <v>36</v>
+      </c>
+      <c r="V5" t="s">
         <v>205</v>
       </c>
-      <c r="C5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="W5" t="s">
         <v>213</v>
-      </c>
-      <c r="G5" t="s">
-        <v>214</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S5" t="s">
-        <v>37</v>
-      </c>
-      <c r="T5" t="s">
-        <v>37</v>
-      </c>
-      <c r="U5" t="s">
-        <v>37</v>
-      </c>
-      <c r="V5" t="s">
-        <v>207</v>
-      </c>
-      <c r="W5" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
         <v>211</v>
       </c>
-      <c r="B6" t="s">
+      <c r="G6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" t="s">
+        <v>36</v>
+      </c>
+      <c r="S6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U6" t="s">
+        <v>36</v>
+      </c>
+      <c r="V6" t="s">
         <v>205</v>
       </c>
-      <c r="C6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" t="s">
-        <v>213</v>
-      </c>
-      <c r="G6" t="s">
-        <v>214</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N6" t="s">
-        <v>37</v>
-      </c>
-      <c r="O6" t="s">
-        <v>37</v>
-      </c>
-      <c r="P6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S6" t="s">
-        <v>37</v>
-      </c>
-      <c r="T6" t="s">
-        <v>37</v>
-      </c>
-      <c r="U6" t="s">
-        <v>37</v>
-      </c>
-      <c r="V6" t="s">
-        <v>207</v>
-      </c>
       <c r="W6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
         <v>211</v>
       </c>
-      <c r="B7" t="s">
+      <c r="G7" t="s">
+        <v>212</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S7" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" t="s">
+        <v>36</v>
+      </c>
+      <c r="U7" t="s">
+        <v>36</v>
+      </c>
+      <c r="V7" t="s">
         <v>205</v>
       </c>
-      <c r="C7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s">
-        <v>213</v>
-      </c>
-      <c r="G7" t="s">
-        <v>214</v>
-      </c>
-      <c r="H7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7" t="s">
-        <v>37</v>
-      </c>
-      <c r="N7" t="s">
-        <v>37</v>
-      </c>
-      <c r="O7" t="s">
-        <v>37</v>
-      </c>
-      <c r="P7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>37</v>
-      </c>
-      <c r="R7" t="s">
-        <v>37</v>
-      </c>
-      <c r="S7" t="s">
-        <v>37</v>
-      </c>
-      <c r="T7" t="s">
-        <v>37</v>
-      </c>
-      <c r="U7" t="s">
-        <v>37</v>
-      </c>
-      <c r="V7" t="s">
-        <v>207</v>
-      </c>
       <c r="W7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>211</v>
+      </c>
+      <c r="G8" t="s">
+        <v>217</v>
+      </c>
+      <c r="H8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" t="s">
+        <v>36</v>
+      </c>
+      <c r="O8" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>36</v>
+      </c>
+      <c r="R8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" t="s">
+        <v>36</v>
+      </c>
+      <c r="U8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V8" t="s">
+        <v>205</v>
+      </c>
+      <c r="W8" t="s">
         <v>218</v>
-      </c>
-      <c r="B8" t="s">
-        <v>205</v>
-      </c>
-      <c r="C8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" t="s">
-        <v>213</v>
-      </c>
-      <c r="G8" t="s">
-        <v>219</v>
-      </c>
-      <c r="H8" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" t="s">
-        <v>37</v>
-      </c>
-      <c r="L8" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" t="s">
-        <v>37</v>
-      </c>
-      <c r="O8" t="s">
-        <v>37</v>
-      </c>
-      <c r="P8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>37</v>
-      </c>
-      <c r="R8" t="s">
-        <v>37</v>
-      </c>
-      <c r="S8" t="s">
-        <v>37</v>
-      </c>
-      <c r="T8" t="s">
-        <v>37</v>
-      </c>
-      <c r="U8" t="s">
-        <v>37</v>
-      </c>
-      <c r="V8" t="s">
-        <v>207</v>
-      </c>
-      <c r="W8" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
+        <v>211</v>
+      </c>
+      <c r="G9" t="s">
+        <v>217</v>
+      </c>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V9" t="s">
         <v>205</v>
       </c>
-      <c r="C9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" t="s">
-        <v>213</v>
-      </c>
-      <c r="G9" t="s">
-        <v>219</v>
-      </c>
-      <c r="H9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O9" t="s">
-        <v>37</v>
-      </c>
-      <c r="P9" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>37</v>
-      </c>
-      <c r="R9" t="s">
-        <v>37</v>
-      </c>
-      <c r="S9" t="s">
-        <v>37</v>
-      </c>
-      <c r="T9" t="s">
-        <v>37</v>
-      </c>
-      <c r="U9" t="s">
-        <v>37</v>
-      </c>
-      <c r="V9" t="s">
-        <v>207</v>
-      </c>
       <c r="W9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" t="s">
+        <v>211</v>
+      </c>
+      <c r="G10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" t="s">
+        <v>36</v>
+      </c>
+      <c r="S10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" t="s">
+        <v>36</v>
+      </c>
+      <c r="U10" t="s">
+        <v>36</v>
+      </c>
+      <c r="V10" t="s">
         <v>205</v>
       </c>
-      <c r="C10" t="s">
-        <v>217</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" t="s">
-        <v>213</v>
-      </c>
-      <c r="G10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" t="s">
-        <v>37</v>
-      </c>
-      <c r="L10" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" t="s">
-        <v>37</v>
-      </c>
-      <c r="N10" t="s">
-        <v>37</v>
-      </c>
-      <c r="O10" t="s">
-        <v>37</v>
-      </c>
-      <c r="P10" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>37</v>
-      </c>
-      <c r="R10" t="s">
-        <v>37</v>
-      </c>
-      <c r="S10" t="s">
-        <v>37</v>
-      </c>
-      <c r="T10" t="s">
-        <v>37</v>
-      </c>
-      <c r="U10" t="s">
-        <v>37</v>
-      </c>
-      <c r="V10" t="s">
-        <v>207</v>
-      </c>
       <c r="W10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" t="s">
         <v>221</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M11" t="s">
+        <v>36</v>
+      </c>
+      <c r="N11" t="s">
+        <v>63</v>
+      </c>
+      <c r="O11" t="s">
+        <v>212</v>
+      </c>
+      <c r="P11" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q11" t="s">
         <v>222</v>
       </c>
-      <c r="C11" t="s">
+      <c r="R11" t="s">
         <v>223</v>
       </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L11" t="s">
-        <v>37</v>
-      </c>
-      <c r="M11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N11" t="s">
-        <v>50</v>
-      </c>
-      <c r="O11" t="s">
-        <v>214</v>
-      </c>
-      <c r="P11" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q11" t="s">
+      <c r="S11" t="s">
         <v>224</v>
       </c>
-      <c r="R11" t="s">
+      <c r="T11" t="s">
+        <v>36</v>
+      </c>
+      <c r="U11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V11" t="s">
+        <v>205</v>
+      </c>
+      <c r="W11" t="s">
         <v>225</v>
-      </c>
-      <c r="S11" t="s">
-        <v>226</v>
-      </c>
-      <c r="T11" t="s">
-        <v>37</v>
-      </c>
-      <c r="U11" t="s">
-        <v>37</v>
-      </c>
-      <c r="V11" t="s">
-        <v>207</v>
-      </c>
-      <c r="W11" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" t="s">
+        <v>36</v>
+      </c>
+      <c r="M12" t="s">
+        <v>36</v>
+      </c>
+      <c r="N12" t="s">
+        <v>63</v>
+      </c>
+      <c r="O12" t="s">
+        <v>212</v>
+      </c>
+      <c r="P12" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q12" t="s">
         <v>222</v>
       </c>
-      <c r="C12" t="s">
-        <v>228</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
-      <c r="I12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L12" t="s">
-        <v>37</v>
-      </c>
-      <c r="M12" t="s">
-        <v>37</v>
-      </c>
-      <c r="N12" t="s">
-        <v>50</v>
-      </c>
-      <c r="O12" t="s">
-        <v>214</v>
-      </c>
-      <c r="P12" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
+        <v>223</v>
+      </c>
+      <c r="S12" t="s">
         <v>224</v>
       </c>
-      <c r="R12" t="s">
-        <v>225</v>
-      </c>
-      <c r="S12" t="s">
-        <v>226</v>
-      </c>
       <c r="T12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B13" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" t="s">
+        <v>227</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" t="s">
+        <v>63</v>
+      </c>
+      <c r="O13" t="s">
+        <v>212</v>
+      </c>
+      <c r="P13" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q13" t="s">
         <v>222</v>
       </c>
-      <c r="C13" t="s">
-        <v>229</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" t="s">
-        <v>37</v>
-      </c>
-      <c r="K13" t="s">
-        <v>37</v>
-      </c>
-      <c r="L13" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" t="s">
-        <v>37</v>
-      </c>
-      <c r="N13" t="s">
-        <v>50</v>
-      </c>
-      <c r="O13" t="s">
-        <v>214</v>
-      </c>
-      <c r="P13" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
+        <v>223</v>
+      </c>
+      <c r="S13" t="s">
         <v>224</v>
       </c>
-      <c r="R13" t="s">
-        <v>225</v>
-      </c>
-      <c r="S13" t="s">
-        <v>226</v>
-      </c>
       <c r="T13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" t="s">
+        <v>36</v>
+      </c>
+      <c r="M14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" t="s">
+        <v>36</v>
+      </c>
+      <c r="O14" t="s">
+        <v>212</v>
+      </c>
+      <c r="P14" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q14" t="s">
         <v>230</v>
       </c>
-      <c r="B14" t="s">
-        <v>222</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" t="s">
-        <v>37</v>
-      </c>
-      <c r="L14" t="s">
-        <v>37</v>
-      </c>
-      <c r="M14" t="s">
-        <v>37</v>
-      </c>
-      <c r="N14" t="s">
-        <v>37</v>
-      </c>
-      <c r="O14" t="s">
-        <v>214</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="R14" t="s">
+        <v>223</v>
+      </c>
+      <c r="S14" t="s">
+        <v>224</v>
+      </c>
+      <c r="T14" t="s">
+        <v>36</v>
+      </c>
+      <c r="U14" t="s">
+        <v>36</v>
+      </c>
+      <c r="V14" t="s">
+        <v>205</v>
+      </c>
+      <c r="W14" t="s">
         <v>231</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>232</v>
-      </c>
-      <c r="R14" t="s">
-        <v>225</v>
-      </c>
-      <c r="S14" t="s">
-        <v>226</v>
-      </c>
-      <c r="T14" t="s">
-        <v>37</v>
-      </c>
-      <c r="U14" t="s">
-        <v>37</v>
-      </c>
-      <c r="V14" t="s">
-        <v>207</v>
-      </c>
-      <c r="W14" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K15" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" t="s">
+        <v>36</v>
+      </c>
+      <c r="M15" t="s">
+        <v>36</v>
+      </c>
+      <c r="N15" t="s">
+        <v>36</v>
+      </c>
+      <c r="O15" t="s">
+        <v>212</v>
+      </c>
+      <c r="P15" t="s">
         <v>234</v>
       </c>
-      <c r="B15" t="s">
-        <v>222</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="Q15" t="s">
         <v>235</v>
       </c>
-      <c r="D15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" t="s">
-        <v>37</v>
-      </c>
-      <c r="L15" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" t="s">
-        <v>37</v>
-      </c>
-      <c r="N15" t="s">
-        <v>37</v>
-      </c>
-      <c r="O15" t="s">
-        <v>214</v>
-      </c>
-      <c r="P15" t="s">
+      <c r="R15" t="s">
         <v>236</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="S15" t="s">
         <v>237</v>
       </c>
-      <c r="R15" t="s">
+      <c r="T15" t="s">
+        <v>36</v>
+      </c>
+      <c r="U15" t="s">
+        <v>36</v>
+      </c>
+      <c r="V15" t="s">
+        <v>205</v>
+      </c>
+      <c r="W15" t="s">
         <v>238</v>
-      </c>
-      <c r="S15" t="s">
-        <v>239</v>
-      </c>
-      <c r="T15" t="s">
-        <v>37</v>
-      </c>
-      <c r="U15" t="s">
-        <v>37</v>
-      </c>
-      <c r="V15" t="s">
-        <v>207</v>
-      </c>
-      <c r="W15" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" t="s">
+        <v>211</v>
+      </c>
+      <c r="G16" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" t="s">
         <v>241</v>
       </c>
-      <c r="B16" t="s">
+      <c r="I16" t="s">
         <v>242</v>
       </c>
-      <c r="C16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" t="s">
-        <v>100</v>
-      </c>
-      <c r="F16" t="s">
-        <v>213</v>
-      </c>
-      <c r="G16" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" t="s">
-        <v>243</v>
-      </c>
-      <c r="I16" t="s">
-        <v>244</v>
-      </c>
       <c r="J16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B17" t="s">
+        <v>240</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" t="s">
+        <v>211</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" t="s">
+        <v>244</v>
+      </c>
+      <c r="I17" t="s">
         <v>242</v>
       </c>
-      <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" t="s">
-        <v>213</v>
-      </c>
-      <c r="G17" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" t="s">
-        <v>246</v>
-      </c>
-      <c r="I17" t="s">
-        <v>244</v>
-      </c>
       <c r="J17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M17" t="s">
         <v>22</v>
       </c>
       <c r="N17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B18" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" t="s">
         <v>247</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" t="s">
+        <v>36</v>
+      </c>
+      <c r="M18" t="s">
+        <v>36</v>
+      </c>
+      <c r="N18" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" t="s">
+        <v>36</v>
+      </c>
+      <c r="P18" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>36</v>
+      </c>
+      <c r="R18" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" t="s">
+        <v>36</v>
+      </c>
+      <c r="U18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V18" t="s">
+        <v>205</v>
+      </c>
+      <c r="W18" t="s">
         <v>248</v>
-      </c>
-      <c r="C18" t="s">
-        <v>249</v>
-      </c>
-      <c r="D18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G18" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I18" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" t="s">
-        <v>37</v>
-      </c>
-      <c r="K18" t="s">
-        <v>37</v>
-      </c>
-      <c r="L18" t="s">
-        <v>37</v>
-      </c>
-      <c r="M18" t="s">
-        <v>37</v>
-      </c>
-      <c r="N18" t="s">
-        <v>37</v>
-      </c>
-      <c r="O18" t="s">
-        <v>37</v>
-      </c>
-      <c r="P18" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>37</v>
-      </c>
-      <c r="R18" t="s">
-        <v>37</v>
-      </c>
-      <c r="S18" t="s">
-        <v>37</v>
-      </c>
-      <c r="T18" t="s">
-        <v>37</v>
-      </c>
-      <c r="U18" t="s">
-        <v>37</v>
-      </c>
-      <c r="V18" t="s">
-        <v>207</v>
-      </c>
-      <c r="W18" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B19" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K19" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L19" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N19" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="O19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V19" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>251</v>
+      </c>
+      <c r="B20" t="s">
+        <v>246</v>
+      </c>
+      <c r="C20" t="s">
+        <v>252</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" t="s">
+        <v>36</v>
+      </c>
+      <c r="K20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" t="s">
+        <v>36</v>
+      </c>
+      <c r="M20" t="s">
+        <v>36</v>
+      </c>
+      <c r="N20" t="s">
+        <v>36</v>
+      </c>
+      <c r="O20" t="s">
+        <v>36</v>
+      </c>
+      <c r="P20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>36</v>
+      </c>
+      <c r="R20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S20" t="s">
+        <v>36</v>
+      </c>
+      <c r="T20" t="s">
+        <v>36</v>
+      </c>
+      <c r="U20" t="s">
+        <v>36</v>
+      </c>
+      <c r="V20" t="s">
+        <v>205</v>
+      </c>
+      <c r="W20" t="s">
         <v>253</v>
-      </c>
-      <c r="B20" t="s">
-        <v>248</v>
-      </c>
-      <c r="C20" t="s">
-        <v>254</v>
-      </c>
-      <c r="D20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" t="s">
-        <v>37</v>
-      </c>
-      <c r="I20" t="s">
-        <v>37</v>
-      </c>
-      <c r="J20" t="s">
-        <v>37</v>
-      </c>
-      <c r="K20" t="s">
-        <v>37</v>
-      </c>
-      <c r="L20" t="s">
-        <v>37</v>
-      </c>
-      <c r="M20" t="s">
-        <v>37</v>
-      </c>
-      <c r="N20" t="s">
-        <v>37</v>
-      </c>
-      <c r="O20" t="s">
-        <v>37</v>
-      </c>
-      <c r="P20" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>37</v>
-      </c>
-      <c r="R20" t="s">
-        <v>37</v>
-      </c>
-      <c r="S20" t="s">
-        <v>37</v>
-      </c>
-      <c r="T20" t="s">
-        <v>37</v>
-      </c>
-      <c r="U20" t="s">
-        <v>37</v>
-      </c>
-      <c r="V20" t="s">
-        <v>207</v>
-      </c>
-      <c r="W20" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J21" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N21" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="O21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V21" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>256</v>
+      </c>
+      <c r="B22" t="s">
+        <v>257</v>
+      </c>
+      <c r="C22" t="s">
         <v>258</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" t="s">
+        <v>36</v>
+      </c>
+      <c r="K22" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" t="s">
+        <v>36</v>
+      </c>
+      <c r="M22" t="s">
+        <v>36</v>
+      </c>
+      <c r="N22" t="s">
+        <v>36</v>
+      </c>
+      <c r="O22" t="s">
+        <v>36</v>
+      </c>
+      <c r="P22" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>36</v>
+      </c>
+      <c r="R22" t="s">
+        <v>36</v>
+      </c>
+      <c r="S22" t="s">
+        <v>36</v>
+      </c>
+      <c r="T22" t="s">
+        <v>36</v>
+      </c>
+      <c r="U22" t="s">
+        <v>36</v>
+      </c>
+      <c r="V22" t="s">
+        <v>205</v>
+      </c>
+      <c r="W22" t="s">
         <v>259</v>
-      </c>
-      <c r="C22" t="s">
-        <v>260</v>
-      </c>
-      <c r="D22" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" t="s">
-        <v>37</v>
-      </c>
-      <c r="H22" t="s">
-        <v>37</v>
-      </c>
-      <c r="I22" t="s">
-        <v>37</v>
-      </c>
-      <c r="J22" t="s">
-        <v>37</v>
-      </c>
-      <c r="K22" t="s">
-        <v>37</v>
-      </c>
-      <c r="L22" t="s">
-        <v>37</v>
-      </c>
-      <c r="M22" t="s">
-        <v>37</v>
-      </c>
-      <c r="N22" t="s">
-        <v>37</v>
-      </c>
-      <c r="O22" t="s">
-        <v>37</v>
-      </c>
-      <c r="P22" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>37</v>
-      </c>
-      <c r="R22" t="s">
-        <v>37</v>
-      </c>
-      <c r="S22" t="s">
-        <v>37</v>
-      </c>
-      <c r="T22" t="s">
-        <v>37</v>
-      </c>
-      <c r="U22" t="s">
-        <v>37</v>
-      </c>
-      <c r="V22" t="s">
-        <v>207</v>
-      </c>
-      <c r="W22" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>260</v>
+      </c>
+      <c r="B23" t="s">
+        <v>261</v>
+      </c>
+      <c r="C23" t="s">
         <v>262</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" t="s">
+        <v>36</v>
+      </c>
+      <c r="J23" t="s">
+        <v>36</v>
+      </c>
+      <c r="K23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" t="s">
+        <v>36</v>
+      </c>
+      <c r="N23" t="s">
+        <v>36</v>
+      </c>
+      <c r="O23" t="s">
+        <v>36</v>
+      </c>
+      <c r="P23" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>36</v>
+      </c>
+      <c r="R23" t="s">
+        <v>36</v>
+      </c>
+      <c r="S23" t="s">
+        <v>36</v>
+      </c>
+      <c r="T23" t="s">
+        <v>36</v>
+      </c>
+      <c r="U23" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" t="s">
+        <v>205</v>
+      </c>
+      <c r="W23" t="s">
         <v>263</v>
-      </c>
-      <c r="C23" t="s">
-        <v>264</v>
-      </c>
-      <c r="D23" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" t="s">
-        <v>37</v>
-      </c>
-      <c r="H23" t="s">
-        <v>37</v>
-      </c>
-      <c r="I23" t="s">
-        <v>37</v>
-      </c>
-      <c r="J23" t="s">
-        <v>37</v>
-      </c>
-      <c r="K23" t="s">
-        <v>37</v>
-      </c>
-      <c r="L23" t="s">
-        <v>37</v>
-      </c>
-      <c r="M23" t="s">
-        <v>37</v>
-      </c>
-      <c r="N23" t="s">
-        <v>37</v>
-      </c>
-      <c r="O23" t="s">
-        <v>37</v>
-      </c>
-      <c r="P23" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>37</v>
-      </c>
-      <c r="R23" t="s">
-        <v>37</v>
-      </c>
-      <c r="S23" t="s">
-        <v>37</v>
-      </c>
-      <c r="T23" t="s">
-        <v>37</v>
-      </c>
-      <c r="U23" t="s">
-        <v>37</v>
-      </c>
-      <c r="V23" t="s">
-        <v>207</v>
-      </c>
-      <c r="W23" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V24" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -6899,122 +6893,122 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" t="s">
         <v>273</v>
       </c>
-      <c r="B5" t="s">
-        <v>275</v>
-      </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -7025,16 +7019,16 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -7042,19 +7036,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -7062,19 +7056,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -7082,33 +7076,33 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -7119,16 +7113,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B12" t="s">
         <v>283</v>
       </c>
-      <c r="B12" t="s">
-        <v>285</v>
-      </c>
       <c r="C12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -7139,16 +7133,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B13" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C13" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -7159,16 +7153,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B14" t="s">
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -7179,16 +7173,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -7199,16 +7193,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -7219,16 +7213,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B17" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17">
         <v>13</v>
@@ -7239,16 +7233,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -7274,90 +7268,90 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web/public/examples/example-with-constraint-rules.xlsx
+++ b/apps/web/public/examples/example-with-constraint-rules.xlsx
@@ -118,7 +118,7 @@
     <t>Musical Patterns II</t>
   </si>
   <si>
-    <t>Kim</t>
+    <t>Kim Mockup</t>
   </si>
   <si>
     <t>Lecture</t>
@@ -265,10 +265,10 @@
     <t>Introduction to Behavioral Dynamics</t>
   </si>
   <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>Lee's two sections are not back to back</t>
+    <t>Lee Standin</t>
+  </si>
+  <si>
+    <t>Lee Standin's two sections are not back to back</t>
   </si>
   <si>
     <t>C</t>
@@ -355,7 +355,7 @@
     <t>Network Optimization</t>
   </si>
   <si>
-    <t>Kim teaches three in a row on MWF</t>
+    <t>Kim Mockup teaches three in a row on MWF</t>
   </si>
   <si>
     <t>318</t>
@@ -736,7 +736,7 @@
     <t>At least one section must meet within the evening hours.</t>
   </si>
   <si>
-    <t>Kim: at most two classes in a row</t>
+    <t>Kim Mockup: at most two classes in a row</t>
   </si>
   <si>
     <t>consecutive</t>
@@ -748,7 +748,7 @@
     <t>20</t>
   </si>
   <si>
-    <t>Lee: at least two classes in a row</t>
+    <t>Lee Standin: at least two classes in a row</t>
   </si>
   <si>
     <t>atLeast</t>
@@ -913,7 +913,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>14:23:18</t>
+    <t>15:09:00</t>
   </si>
   <si>
     <t>Academic Year</t>
